--- a/desk_backtest.xlsx
+++ b/desk_backtest.xlsx
@@ -5211,22 +5211,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
-        <v>9.31</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
       <c r="V6">
         <f>(I6-O6)^2+(J6-P6)^2+(K6-Q6)^2</f>
         <v/>
@@ -5299,22 +5288,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U7" t="n">
-        <v>9.31</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
       <c r="V7">
         <f>(I7-O7)^2+(J7-P7)^2+(K7-Q7)^2</f>
         <v/>
@@ -5387,22 +5365,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U8" t="n">
-        <v>9.31</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
       <c r="V8">
         <f>(I8-O8)^2+(J8-P8)^2+(K8-Q8)^2</f>
         <v/>
@@ -5475,22 +5442,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U9" t="n">
-        <v>9.31</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
       <c r="V9">
         <f>(I9-O9)^2+(J9-P9)^2+(K9-Q9)^2</f>
         <v/>
@@ -5563,22 +5519,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U10" t="n">
-        <v>16.73</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
       <c r="V10">
         <f>(I10-O10)^2+(J10-P10)^2+(K10-Q10)^2</f>
         <v/>
@@ -5651,22 +5596,11 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U11" t="n">
-        <v>16.73</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
       <c r="V11">
         <f>(I11-O11)^2+(J11-P11)^2+(K11-Q11)^2</f>
         <v/>
@@ -5739,22 +5673,11 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U12" t="n">
-        <v>16.73</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
       <c r="V12">
         <f>(I12-O12)^2+(J12-P12)^2+(K12-Q12)^2</f>
         <v/>
@@ -5827,22 +5750,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U13" t="n">
-        <v>16.73</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
       <c r="V13">
         <f>(I13-O13)^2+(J13-P13)^2+(K13-Q13)^2</f>
         <v/>
@@ -6223,22 +6135,11 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U18" t="n">
-        <v>3.83</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
       <c r="V18">
         <f>(I18-O18)^2+(J18-P18)^2+(K18-Q18)^2</f>
         <v/>
@@ -6311,22 +6212,11 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U19" t="n">
-        <v>3.83</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
       <c r="V19">
         <f>(I19-O19)^2+(J19-P19)^2+(K19-Q19)^2</f>
         <v/>
@@ -6399,22 +6289,11 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U20" t="n">
-        <v>3.83</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
       <c r="V20">
         <f>(I20-O20)^2+(J20-P20)^2+(K20-Q20)^2</f>
         <v/>
@@ -6487,22 +6366,11 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U21" t="n">
-        <v>3.83</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
       <c r="V21">
         <f>(I21-O21)^2+(J21-P21)^2+(K21-Q21)^2</f>
         <v/>
@@ -6575,22 +6443,11 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U22" t="n">
-        <v>4.34</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
       <c r="V22">
         <f>(I22-O22)^2+(J22-P22)^2+(K22-Q22)^2</f>
         <v/>
@@ -6663,22 +6520,11 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U23" t="n">
-        <v>4.34</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
       <c r="V23">
         <f>(I23-O23)^2+(J23-P23)^2+(K23-Q23)^2</f>
         <v/>
@@ -6751,22 +6597,11 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U24" t="n">
-        <v>4.34</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
       <c r="V24">
         <f>(I24-O24)^2+(J24-P24)^2+(K24-Q24)^2</f>
         <v/>
@@ -6839,22 +6674,11 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U25" t="n">
-        <v>4.34</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
       <c r="V25">
         <f>(I25-O25)^2+(J25-P25)^2+(K25-Q25)^2</f>
         <v/>
@@ -7235,22 +7059,11 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U30" t="n">
-        <v>9.84</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
       <c r="V30">
         <f>(I30-O30)^2+(J30-P30)^2+(K30-Q30)^2</f>
         <v/>
@@ -7323,22 +7136,11 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U31" t="n">
-        <v>9.84</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
       <c r="V31">
         <f>(I31-O31)^2+(J31-P31)^2+(K31-Q31)^2</f>
         <v/>
@@ -7411,22 +7213,11 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U32" t="n">
-        <v>9.84</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
       <c r="V32">
         <f>(I32-O32)^2+(J32-P32)^2+(K32-Q32)^2</f>
         <v/>
@@ -7499,22 +7290,11 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U33" t="n">
-        <v>9.84</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
       <c r="V33">
         <f>(I33-O33)^2+(J33-P33)^2+(K33-Q33)^2</f>
         <v/>
@@ -7587,22 +7367,11 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U34" t="n">
-        <v>7.02</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
       <c r="V34">
         <f>(I34-O34)^2+(J34-P34)^2+(K34-Q34)^2</f>
         <v/>
@@ -7675,22 +7444,11 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U35" t="n">
-        <v>7.02</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
       <c r="V35">
         <f>(I35-O35)^2+(J35-P35)^2+(K35-Q35)^2</f>
         <v/>
@@ -7763,22 +7521,11 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U36" t="n">
-        <v>7.02</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
       <c r="V36">
         <f>(I36-O36)^2+(J36-P36)^2+(K36-Q36)^2</f>
         <v/>
@@ -7851,22 +7598,11 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U37" t="n">
-        <v>7.02</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
       <c r="V37">
         <f>(I37-O37)^2+(J37-P37)^2+(K37-Q37)^2</f>
         <v/>
@@ -8643,22 +8379,11 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U46" t="n">
-        <v>10.46</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
       <c r="V46">
         <f>(I46-O46)^2+(J46-P46)^2+(K46-Q46)^2</f>
         <v/>
@@ -8731,22 +8456,11 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U47" t="n">
-        <v>10.46</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
       <c r="V47">
         <f>(I47-O47)^2+(J47-P47)^2+(K47-Q47)^2</f>
         <v/>
@@ -8819,22 +8533,11 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U48" t="n">
-        <v>10.46</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
       <c r="V48">
         <f>(I48-O48)^2+(J48-P48)^2+(K48-Q48)^2</f>
         <v/>
@@ -8907,22 +8610,11 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U49" t="n">
-        <v>10.46</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
       <c r="V49">
         <f>(I49-O49)^2+(J49-P49)^2+(K49-Q49)^2</f>
         <v/>
@@ -8995,22 +8687,11 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U50" t="n">
-        <v>4.6</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
       <c r="V50">
         <f>(I50-O50)^2+(J50-P50)^2+(K50-Q50)^2</f>
         <v/>
@@ -9083,22 +8764,11 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U51" t="n">
-        <v>4.6</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
       <c r="V51">
         <f>(I51-O51)^2+(J51-P51)^2+(K51-Q51)^2</f>
         <v/>
@@ -9171,22 +8841,11 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U52" t="n">
-        <v>4.6</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
       <c r="V52">
         <f>(I52-O52)^2+(J52-P52)^2+(K52-Q52)^2</f>
         <v/>
@@ -9259,22 +8918,11 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U53" t="n">
-        <v>4.6</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
       <c r="V53">
         <f>(I53-O53)^2+(J53-P53)^2+(K53-Q53)^2</f>
         <v/>
@@ -9347,22 +8995,11 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U54" t="n">
-        <v>6.22</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
       <c r="V54">
         <f>(I54-O54)^2+(J54-P54)^2+(K54-Q54)^2</f>
         <v/>
@@ -9435,22 +9072,11 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U55" t="n">
-        <v>6.22</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
       <c r="V55">
         <f>(I55-O55)^2+(J55-P55)^2+(K55-Q55)^2</f>
         <v/>
@@ -9523,22 +9149,11 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U56" t="n">
-        <v>6.22</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
       <c r="V56">
         <f>(I56-O56)^2+(J56-P56)^2+(K56-Q56)^2</f>
         <v/>
@@ -9611,22 +9226,11 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U57" t="n">
-        <v>6.22</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
       <c r="V57">
         <f>(I57-O57)^2+(J57-P57)^2+(K57-Q57)^2</f>
         <v/>
@@ -9699,22 +9303,11 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U58" t="n">
-        <v>12.89</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
       <c r="V58">
         <f>(I58-O58)^2+(J58-P58)^2+(K58-Q58)^2</f>
         <v/>
@@ -9787,22 +9380,11 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U59" t="n">
-        <v>12.89</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
       <c r="V59">
         <f>(I59-O59)^2+(J59-P59)^2+(K59-Q59)^2</f>
         <v/>
@@ -9875,22 +9457,11 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U60" t="n">
-        <v>12.89</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
       <c r="V60">
         <f>(I60-O60)^2+(J60-P60)^2+(K60-Q60)^2</f>
         <v/>
@@ -9963,22 +9534,11 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U61" t="n">
-        <v>12.89</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
       <c r="V61">
         <f>(I61-O61)^2+(J61-P61)^2+(K61-Q61)^2</f>
         <v/>
@@ -10403,22 +9963,11 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U66" t="n">
-        <v>9.69</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
       <c r="V66">
         <f>(I66-O66)^2+(J66-P66)^2+(K66-Q66)^2</f>
         <v/>
@@ -10491,22 +10040,11 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U67" t="n">
-        <v>9.69</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
       <c r="V67">
         <f>(I67-O67)^2+(J67-P67)^2+(K67-Q67)^2</f>
         <v/>
@@ -10579,22 +10117,11 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U68" t="n">
-        <v>9.69</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
       <c r="V68">
         <f>(I68-O68)^2+(J68-P68)^2+(K68-Q68)^2</f>
         <v/>
@@ -10667,22 +10194,11 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U69" t="n">
-        <v>9.69</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
       <c r="V69">
         <f>(I69-O69)^2+(J69-P69)^2+(K69-Q69)^2</f>
         <v/>
@@ -10755,22 +10271,11 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U70" t="n">
-        <v>4.22</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
       <c r="V70">
         <f>(I70-O70)^2+(J70-P70)^2+(K70-Q70)^2</f>
         <v/>
@@ -10843,22 +10348,11 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U71" t="n">
-        <v>4.22</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
       <c r="V71">
         <f>(I71-O71)^2+(J71-P71)^2+(K71-Q71)^2</f>
         <v/>
@@ -10931,22 +10425,11 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U72" t="n">
-        <v>4.22</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
       <c r="V72">
         <f>(I72-O72)^2+(J72-P72)^2+(K72-Q72)^2</f>
         <v/>
@@ -11019,22 +10502,11 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U73" t="n">
-        <v>4.22</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
       <c r="V73">
         <f>(I73-O73)^2+(J73-P73)^2+(K73-Q73)^2</f>
         <v/>
@@ -11107,22 +10579,11 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U74" t="n">
-        <v>6.49</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
       <c r="V74">
         <f>(I74-O74)^2+(J74-P74)^2+(K74-Q74)^2</f>
         <v/>
@@ -11195,22 +10656,11 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U75" t="n">
-        <v>6.49</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
       <c r="V75">
         <f>(I75-O75)^2+(J75-P75)^2+(K75-Q75)^2</f>
         <v/>
@@ -11283,22 +10733,11 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U76" t="n">
-        <v>6.49</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
       <c r="V76">
         <f>(I76-O76)^2+(J76-P76)^2+(K76-Q76)^2</f>
         <v/>
@@ -11371,22 +10810,11 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U77" t="n">
-        <v>6.49</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
       <c r="V77">
         <f>(I77-O77)^2+(J77-P77)^2+(K77-Q77)^2</f>
         <v/>
@@ -11459,22 +10887,11 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U78" t="n">
-        <v>5.97</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
       <c r="V78">
         <f>(I78-O78)^2+(J78-P78)^2+(K78-Q78)^2</f>
         <v/>
@@ -11547,22 +10964,11 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U79" t="n">
-        <v>5.97</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
       <c r="V79">
         <f>(I79-O79)^2+(J79-P79)^2+(K79-Q79)^2</f>
         <v/>
@@ -11635,22 +11041,11 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U80" t="n">
-        <v>5.97</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
       <c r="V80">
         <f>(I80-O80)^2+(J80-P80)^2+(K80-Q80)^2</f>
         <v/>
@@ -11723,22 +11118,11 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U81" t="n">
-        <v>5.97</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
       <c r="V81">
         <f>(I81-O81)^2+(J81-P81)^2+(K81-Q81)^2</f>
         <v/>
@@ -11811,22 +11195,11 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U82" t="n">
-        <v>6.7</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
       <c r="V82">
         <f>(I82-O82)^2+(J82-P82)^2+(K82-Q82)^2</f>
         <v/>
@@ -11899,22 +11272,11 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U83" t="n">
-        <v>6.7</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
       <c r="V83">
         <f>(I83-O83)^2+(J83-P83)^2+(K83-Q83)^2</f>
         <v/>
@@ -11987,22 +11349,11 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U84" t="n">
-        <v>6.7</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
       <c r="V84">
         <f>(I84-O84)^2+(J84-P84)^2+(K84-Q84)^2</f>
         <v/>
@@ -12075,22 +11426,11 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U85" t="n">
-        <v>6.7</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
       <c r="V85">
         <f>(I85-O85)^2+(J85-P85)^2+(K85-Q85)^2</f>
         <v/>
@@ -12163,22 +11503,11 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U86" t="n">
-        <v>9.94</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
       <c r="V86">
         <f>(I86-O86)^2+(J86-P86)^2+(K86-Q86)^2</f>
         <v/>
@@ -12251,22 +11580,11 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U87" t="n">
-        <v>9.94</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
       <c r="V87">
         <f>(I87-O87)^2+(J87-P87)^2+(K87-Q87)^2</f>
         <v/>
@@ -12339,22 +11657,11 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U88" t="n">
-        <v>9.94</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
       <c r="V88">
         <f>(I88-O88)^2+(J88-P88)^2+(K88-Q88)^2</f>
         <v/>
@@ -12427,22 +11734,11 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U89" t="n">
-        <v>9.94</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
       <c r="V89">
         <f>(I89-O89)^2+(J89-P89)^2+(K89-Q89)^2</f>
         <v/>
@@ -12515,22 +11811,11 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U90" t="n">
-        <v>8.44</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
       <c r="V90">
         <f>(I90-O90)^2+(J90-P90)^2+(K90-Q90)^2</f>
         <v/>
@@ -12603,22 +11888,11 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U91" t="n">
-        <v>8.44</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
       <c r="V91">
         <f>(I91-O91)^2+(J91-P91)^2+(K91-Q91)^2</f>
         <v/>
@@ -12691,22 +11965,11 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U92" t="n">
-        <v>8.44</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
       <c r="V92">
         <f>(I92-O92)^2+(J92-P92)^2+(K92-Q92)^2</f>
         <v/>
@@ -12779,22 +12042,11 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U93" t="n">
-        <v>8.44</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
       <c r="V93">
         <f>(I93-O93)^2+(J93-P93)^2+(K93-Q93)^2</f>
         <v/>
@@ -12867,22 +12119,11 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U94" t="n">
-        <v>8.550000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
       <c r="V94">
         <f>(I94-O94)^2+(J94-P94)^2+(K94-Q94)^2</f>
         <v/>
@@ -12955,22 +12196,11 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U95" t="n">
-        <v>8.550000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
       <c r="V95">
         <f>(I95-O95)^2+(J95-P95)^2+(K95-Q95)^2</f>
         <v/>
@@ -13043,22 +12273,11 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U96" t="n">
-        <v>8.550000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
       <c r="V96">
         <f>(I96-O96)^2+(J96-P96)^2+(K96-Q96)^2</f>
         <v/>
@@ -13131,22 +12350,11 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U97" t="n">
-        <v>8.550000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
       <c r="V97">
         <f>(I97-O97)^2+(J97-P97)^2+(K97-Q97)^2</f>
         <v/>
@@ -13219,22 +12427,11 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>Costa Rica</t>
-        </is>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U98" t="n">
-        <v>9.84</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
       <c r="V98">
         <f>(I98-O98)^2+(J98-P98)^2+(K98-Q98)^2</f>
         <v/>
@@ -13307,22 +12504,11 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>Costa Rica</t>
-        </is>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U99" t="n">
-        <v>9.84</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
       <c r="V99">
         <f>(I99-O99)^2+(J99-P99)^2+(K99-Q99)^2</f>
         <v/>
@@ -13395,22 +12581,11 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>Costa Rica</t>
-        </is>
-      </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U100" t="n">
-        <v>9.84</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
       <c r="V100">
         <f>(I100-O100)^2+(J100-P100)^2+(K100-Q100)^2</f>
         <v/>
@@ -13483,22 +12658,11 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>Costa Rica</t>
-        </is>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U101" t="n">
-        <v>9.84</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
       <c r="V101">
         <f>(I101-O101)^2+(J101-P101)^2+(K101-Q101)^2</f>
         <v/>
@@ -13571,22 +12735,11 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U102" t="n">
-        <v>10.36</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
       <c r="V102">
         <f>(I102-O102)^2+(J102-P102)^2+(K102-Q102)^2</f>
         <v/>
@@ -13659,22 +12812,11 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U103" t="n">
-        <v>10.36</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
       <c r="V103">
         <f>(I103-O103)^2+(J103-P103)^2+(K103-Q103)^2</f>
         <v/>
@@ -13747,22 +12889,11 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T104" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U104" t="n">
-        <v>10.36</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
       <c r="V104">
         <f>(I104-O104)^2+(J104-P104)^2+(K104-Q104)^2</f>
         <v/>
@@ -13835,22 +12966,11 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T105" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U105" t="n">
-        <v>10.36</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
       <c r="V105">
         <f>(I105-O105)^2+(J105-P105)^2+(K105-Q105)^2</f>
         <v/>
@@ -13923,22 +13043,11 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U106" t="n">
-        <v>4.42</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
       <c r="V106">
         <f>(I106-O106)^2+(J106-P106)^2+(K106-Q106)^2</f>
         <v/>
@@ -14011,22 +13120,11 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="T107" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U107" t="n">
-        <v>4.42</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
       <c r="V107">
         <f>(I107-O107)^2+(J107-P107)^2+(K107-Q107)^2</f>
         <v/>
@@ -14099,22 +13197,11 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U108" t="n">
-        <v>4.42</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
       <c r="V108">
         <f>(I108-O108)^2+(J108-P108)^2+(K108-Q108)^2</f>
         <v/>
@@ -14187,22 +13274,11 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U109" t="n">
-        <v>4.42</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
       <c r="V109">
         <f>(I109-O109)^2+(J109-P109)^2+(K109-Q109)^2</f>
         <v/>
@@ -14275,22 +13351,11 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U110" t="n">
-        <v>13.58</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
       <c r="V110">
         <f>(I110-O110)^2+(J110-P110)^2+(K110-Q110)^2</f>
         <v/>
@@ -14363,22 +13428,11 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="T111" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U111" t="n">
-        <v>13.58</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
       <c r="V111">
         <f>(I111-O111)^2+(J111-P111)^2+(K111-Q111)^2</f>
         <v/>
@@ -14451,22 +13505,11 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="T112" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U112" t="n">
-        <v>13.58</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
       <c r="V112">
         <f>(I112-O112)^2+(J112-P112)^2+(K112-Q112)^2</f>
         <v/>
@@ -14539,22 +13582,11 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U113" t="n">
-        <v>13.58</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
       <c r="V113">
         <f>(I113-O113)^2+(J113-P113)^2+(K113-Q113)^2</f>
         <v/>
@@ -14627,22 +13659,11 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="T114" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U114" t="n">
-        <v>5.39</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
       <c r="V114">
         <f>(I114-O114)^2+(J114-P114)^2+(K114-Q114)^2</f>
         <v/>
@@ -14715,22 +13736,11 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="T115" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U115" t="n">
-        <v>5.39</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
       <c r="V115">
         <f>(I115-O115)^2+(J115-P115)^2+(K115-Q115)^2</f>
         <v/>
@@ -14803,22 +13813,11 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U116" t="n">
-        <v>5.39</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
       <c r="V116">
         <f>(I116-O116)^2+(J116-P116)^2+(K116-Q116)^2</f>
         <v/>
@@ -14891,22 +13890,11 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="T117" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U117" t="n">
-        <v>5.39</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
       <c r="V117">
         <f>(I117-O117)^2+(J117-P117)^2+(K117-Q117)^2</f>
         <v/>
@@ -14979,22 +13967,11 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="T118" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U118" t="n">
-        <v>4.48</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
       <c r="V118">
         <f>(I118-O118)^2+(J118-P118)^2+(K118-Q118)^2</f>
         <v/>
@@ -15067,22 +14044,11 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="T119" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U119" t="n">
-        <v>4.48</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
       <c r="V119">
         <f>(I119-O119)^2+(J119-P119)^2+(K119-Q119)^2</f>
         <v/>
@@ -15155,22 +14121,11 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U120" t="n">
-        <v>4.48</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
       <c r="V120">
         <f>(I120-O120)^2+(J120-P120)^2+(K120-Q120)^2</f>
         <v/>
@@ -15243,22 +14198,11 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U121" t="n">
-        <v>4.48</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
       <c r="V121">
         <f>(I121-O121)^2+(J121-P121)^2+(K121-Q121)^2</f>
         <v/>
@@ -15331,22 +14275,11 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T122" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U122" t="n">
-        <v>11.17</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
       <c r="V122">
         <f>(I122-O122)^2+(J122-P122)^2+(K122-Q122)^2</f>
         <v/>
@@ -15419,22 +14352,11 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T123" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U123" t="n">
-        <v>11.17</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
       <c r="V123">
         <f>(I123-O123)^2+(J123-P123)^2+(K123-Q123)^2</f>
         <v/>
@@ -15507,22 +14429,11 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T124" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U124" t="n">
-        <v>11.17</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
       <c r="V124">
         <f>(I124-O124)^2+(J124-P124)^2+(K124-Q124)^2</f>
         <v/>
@@ -15595,22 +14506,11 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U125" t="n">
-        <v>11.17</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
       <c r="V125">
         <f>(I125-O125)^2+(J125-P125)^2+(K125-Q125)^2</f>
         <v/>
@@ -15683,22 +14583,11 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U126" t="n">
-        <v>9.609999999999999</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr"/>
       <c r="V126">
         <f>(I126-O126)^2+(J126-P126)^2+(K126-Q126)^2</f>
         <v/>
@@ -15771,22 +14660,11 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U127" t="n">
-        <v>9.609999999999999</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr"/>
       <c r="V127">
         <f>(I127-O127)^2+(J127-P127)^2+(K127-Q127)^2</f>
         <v/>
@@ -15859,22 +14737,11 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U128" t="n">
-        <v>9.609999999999999</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr"/>
       <c r="V128">
         <f>(I128-O128)^2+(J128-P128)^2+(K128-Q128)^2</f>
         <v/>
@@ -15947,22 +14814,11 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T129" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U129" t="n">
-        <v>9.609999999999999</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr"/>
       <c r="V129">
         <f>(I129-O129)^2+(J129-P129)^2+(K129-Q129)^2</f>
         <v/>
@@ -16387,22 +15243,11 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U134" t="n">
-        <v>9.210000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr"/>
       <c r="V134">
         <f>(I134-O134)^2+(J134-P134)^2+(K134-Q134)^2</f>
         <v/>
@@ -16475,22 +15320,11 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="T135" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U135" t="n">
-        <v>9.210000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
       <c r="V135">
         <f>(I135-O135)^2+(J135-P135)^2+(K135-Q135)^2</f>
         <v/>
@@ -16563,22 +15397,11 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="T136" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U136" t="n">
-        <v>9.210000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr"/>
       <c r="V136">
         <f>(I136-O136)^2+(J136-P136)^2+(K136-Q136)^2</f>
         <v/>
@@ -16651,22 +15474,11 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="T137" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U137" t="n">
-        <v>9.210000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
       <c r="V137">
         <f>(I137-O137)^2+(J137-P137)^2+(K137-Q137)^2</f>
         <v/>
@@ -16739,22 +15551,11 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>Wales</t>
-        </is>
-      </c>
-      <c r="T138" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U138" t="n">
-        <v>4.92</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr"/>
       <c r="V138">
         <f>(I138-O138)^2+(J138-P138)^2+(K138-Q138)^2</f>
         <v/>
@@ -16827,22 +15628,11 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>Wales</t>
-        </is>
-      </c>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U139" t="n">
-        <v>4.92</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr"/>
+      <c r="T139" t="inlineStr"/>
       <c r="V139">
         <f>(I139-O139)^2+(J139-P139)^2+(K139-Q139)^2</f>
         <v/>
@@ -16915,22 +15705,11 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>Wales</t>
-        </is>
-      </c>
-      <c r="T140" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U140" t="n">
-        <v>4.92</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr"/>
+      <c r="T140" t="inlineStr"/>
       <c r="V140">
         <f>(I140-O140)^2+(J140-P140)^2+(K140-Q140)^2</f>
         <v/>
@@ -17003,22 +15782,11 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>Wales</t>
-        </is>
-      </c>
-      <c r="T141" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U141" t="n">
-        <v>4.92</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr"/>
+      <c r="T141" t="inlineStr"/>
       <c r="V141">
         <f>(I141-O141)^2+(J141-P141)^2+(K141-Q141)^2</f>
         <v/>
@@ -17443,22 +16211,11 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T146" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U146" t="n">
-        <v>12.34</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr"/>
       <c r="V146">
         <f>(I146-O146)^2+(J146-P146)^2+(K146-Q146)^2</f>
         <v/>
@@ -17531,22 +16288,11 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T147" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U147" t="n">
-        <v>12.34</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr"/>
       <c r="V147">
         <f>(I147-O147)^2+(J147-P147)^2+(K147-Q147)^2</f>
         <v/>
@@ -17619,22 +16365,11 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T148" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U148" t="n">
-        <v>12.34</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr"/>
       <c r="V148">
         <f>(I148-O148)^2+(J148-P148)^2+(K148-Q148)^2</f>
         <v/>
@@ -17707,22 +16442,11 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T149" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U149" t="n">
-        <v>12.34</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr"/>
       <c r="V149">
         <f>(I149-O149)^2+(J149-P149)^2+(K149-Q149)^2</f>
         <v/>
@@ -17795,22 +16519,11 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="T150" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U150" t="n">
-        <v>9.640000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr"/>
       <c r="V150">
         <f>(I150-O150)^2+(J150-P150)^2+(K150-Q150)^2</f>
         <v/>
@@ -17883,22 +16596,11 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="T151" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U151" t="n">
-        <v>9.640000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr"/>
       <c r="V151">
         <f>(I151-O151)^2+(J151-P151)^2+(K151-Q151)^2</f>
         <v/>
@@ -17971,22 +16673,11 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="T152" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U152" t="n">
-        <v>9.640000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr"/>
+      <c r="T152" t="inlineStr"/>
       <c r="V152">
         <f>(I152-O152)^2+(J152-P152)^2+(K152-Q152)^2</f>
         <v/>
@@ -18059,22 +16750,11 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="T153" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U153" t="n">
-        <v>9.640000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="inlineStr"/>
       <c r="V153">
         <f>(I153-O153)^2+(J153-P153)^2+(K153-Q153)^2</f>
         <v/>
@@ -18147,22 +16827,11 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T154" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U154" t="n">
-        <v>6.34</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="inlineStr"/>
       <c r="V154">
         <f>(I154-O154)^2+(J154-P154)^2+(K154-Q154)^2</f>
         <v/>
@@ -18235,22 +16904,11 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T155" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U155" t="n">
-        <v>6.34</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="inlineStr"/>
       <c r="V155">
         <f>(I155-O155)^2+(J155-P155)^2+(K155-Q155)^2</f>
         <v/>
@@ -18323,22 +16981,11 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T156" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U156" t="n">
-        <v>6.34</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="inlineStr"/>
       <c r="V156">
         <f>(I156-O156)^2+(J156-P156)^2+(K156-Q156)^2</f>
         <v/>
@@ -18411,22 +17058,11 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T157" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U157" t="n">
-        <v>6.34</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="inlineStr"/>
       <c r="V157">
         <f>(I157-O157)^2+(J157-P157)^2+(K157-Q157)^2</f>
         <v/>
@@ -18499,22 +17135,11 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="T158" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U158" t="n">
-        <v>11.86</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="inlineStr"/>
       <c r="V158">
         <f>(I158-O158)^2+(J158-P158)^2+(K158-Q158)^2</f>
         <v/>
@@ -18587,22 +17212,11 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="T159" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U159" t="n">
-        <v>11.86</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr"/>
       <c r="V159">
         <f>(I159-O159)^2+(J159-P159)^2+(K159-Q159)^2</f>
         <v/>
@@ -18675,22 +17289,11 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="T160" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U160" t="n">
-        <v>11.86</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr"/>
       <c r="V160">
         <f>(I160-O160)^2+(J160-P160)^2+(K160-Q160)^2</f>
         <v/>
@@ -18763,22 +17366,11 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="T161" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U161" t="n">
-        <v>11.86</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr"/>
       <c r="V161">
         <f>(I161-O161)^2+(J161-P161)^2+(K161-Q161)^2</f>
         <v/>
@@ -18851,22 +17443,11 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T162" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U162" t="n">
-        <v>7.66</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr"/>
       <c r="V162">
         <f>(I162-O162)^2+(J162-P162)^2+(K162-Q162)^2</f>
         <v/>
@@ -18939,22 +17520,11 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T163" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U163" t="n">
-        <v>7.66</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr"/>
+      <c r="T163" t="inlineStr"/>
       <c r="V163">
         <f>(I163-O163)^2+(J163-P163)^2+(K163-Q163)^2</f>
         <v/>
@@ -19027,22 +17597,11 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T164" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U164" t="n">
-        <v>7.66</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr"/>
+      <c r="T164" t="inlineStr"/>
       <c r="V164">
         <f>(I164-O164)^2+(J164-P164)^2+(K164-Q164)^2</f>
         <v/>
@@ -19115,22 +17674,11 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T165" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U165" t="n">
-        <v>7.66</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="inlineStr"/>
       <c r="V165">
         <f>(I165-O165)^2+(J165-P165)^2+(K165-Q165)^2</f>
         <v/>
@@ -19203,22 +17751,11 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="T166" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U166" t="n">
-        <v>7.96</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr"/>
+      <c r="T166" t="inlineStr"/>
       <c r="V166">
         <f>(I166-O166)^2+(J166-P166)^2+(K166-Q166)^2</f>
         <v/>
@@ -19291,22 +17828,11 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="T167" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U167" t="n">
-        <v>7.96</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr"/>
+      <c r="T167" t="inlineStr"/>
       <c r="V167">
         <f>(I167-O167)^2+(J167-P167)^2+(K167-Q167)^2</f>
         <v/>
@@ -19379,22 +17905,11 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="T168" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U168" t="n">
-        <v>7.96</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr"/>
+      <c r="T168" t="inlineStr"/>
       <c r="V168">
         <f>(I168-O168)^2+(J168-P168)^2+(K168-Q168)^2</f>
         <v/>
@@ -19467,22 +17982,11 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="T169" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U169" t="n">
-        <v>7.96</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr"/>
+      <c r="T169" t="inlineStr"/>
       <c r="V169">
         <f>(I169-O169)^2+(J169-P169)^2+(K169-Q169)^2</f>
         <v/>
@@ -19555,22 +18059,11 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="T170" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U170" t="n">
-        <v>3.5</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr"/>
+      <c r="T170" t="inlineStr"/>
       <c r="V170">
         <f>(I170-O170)^2+(J170-P170)^2+(K170-Q170)^2</f>
         <v/>
@@ -19643,22 +18136,11 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="T171" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U171" t="n">
-        <v>3.5</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr"/>
+      <c r="T171" t="inlineStr"/>
       <c r="V171">
         <f>(I171-O171)^2+(J171-P171)^2+(K171-Q171)^2</f>
         <v/>
@@ -19731,22 +18213,11 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="T172" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U172" t="n">
-        <v>3.5</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr"/>
+      <c r="T172" t="inlineStr"/>
       <c r="V172">
         <f>(I172-O172)^2+(J172-P172)^2+(K172-Q172)^2</f>
         <v/>
@@ -19819,22 +18290,11 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="T173" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U173" t="n">
-        <v>3.5</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr"/>
+      <c r="T173" t="inlineStr"/>
       <c r="V173">
         <f>(I173-O173)^2+(J173-P173)^2+(K173-Q173)^2</f>
         <v/>
@@ -20259,22 +18719,11 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T178" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U178" t="n">
-        <v>14.24</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr"/>
+      <c r="T178" t="inlineStr"/>
       <c r="V178">
         <f>(I178-O178)^2+(J178-P178)^2+(K178-Q178)^2</f>
         <v/>
@@ -20347,22 +18796,11 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T179" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U179" t="n">
-        <v>14.24</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr"/>
+      <c r="T179" t="inlineStr"/>
       <c r="V179">
         <f>(I179-O179)^2+(J179-P179)^2+(K179-Q179)^2</f>
         <v/>
@@ -20435,22 +18873,11 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T180" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U180" t="n">
-        <v>14.24</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr"/>
+      <c r="T180" t="inlineStr"/>
       <c r="V180">
         <f>(I180-O180)^2+(J180-P180)^2+(K180-Q180)^2</f>
         <v/>
@@ -20523,22 +18950,11 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T181" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U181" t="n">
-        <v>14.24</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr"/>
+      <c r="T181" t="inlineStr"/>
       <c r="V181">
         <f>(I181-O181)^2+(J181-P181)^2+(K181-Q181)^2</f>
         <v/>
@@ -20611,22 +19027,11 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="T182" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U182" t="n">
-        <v>11.26</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr"/>
+      <c r="T182" t="inlineStr"/>
       <c r="V182">
         <f>(I182-O182)^2+(J182-P182)^2+(K182-Q182)^2</f>
         <v/>
@@ -20699,22 +19104,11 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="T183" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U183" t="n">
-        <v>11.26</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr"/>
+      <c r="T183" t="inlineStr"/>
       <c r="V183">
         <f>(I183-O183)^2+(J183-P183)^2+(K183-Q183)^2</f>
         <v/>
@@ -20787,22 +19181,11 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="T184" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U184" t="n">
-        <v>11.26</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr"/>
+      <c r="T184" t="inlineStr"/>
       <c r="V184">
         <f>(I184-O184)^2+(J184-P184)^2+(K184-Q184)^2</f>
         <v/>
@@ -20875,22 +19258,11 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="T185" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U185" t="n">
-        <v>11.26</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr"/>
+      <c r="T185" t="inlineStr"/>
       <c r="V185">
         <f>(I185-O185)^2+(J185-P185)^2+(K185-Q185)^2</f>
         <v/>
@@ -20963,22 +19335,11 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T186" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U186" t="n">
-        <v>7.72</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr"/>
+      <c r="T186" t="inlineStr"/>
       <c r="V186">
         <f>(I186-O186)^2+(J186-P186)^2+(K186-Q186)^2</f>
         <v/>
@@ -21051,22 +19412,11 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T187" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U187" t="n">
-        <v>7.72</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr"/>
+      <c r="T187" t="inlineStr"/>
       <c r="V187">
         <f>(I187-O187)^2+(J187-P187)^2+(K187-Q187)^2</f>
         <v/>
@@ -21139,22 +19489,11 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T188" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U188" t="n">
-        <v>7.72</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr"/>
+      <c r="T188" t="inlineStr"/>
       <c r="V188">
         <f>(I188-O188)^2+(J188-P188)^2+(K188-Q188)^2</f>
         <v/>
@@ -21227,22 +19566,11 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T189" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U189" t="n">
-        <v>7.72</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr"/>
+      <c r="T189" t="inlineStr"/>
       <c r="V189">
         <f>(I189-O189)^2+(J189-P189)^2+(K189-Q189)^2</f>
         <v/>
@@ -21315,22 +19643,11 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="T190" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U190" t="n">
-        <v>7.87</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr"/>
+      <c r="T190" t="inlineStr"/>
       <c r="V190">
         <f>(I190-O190)^2+(J190-P190)^2+(K190-Q190)^2</f>
         <v/>
@@ -21403,22 +19720,11 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="T191" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U191" t="n">
-        <v>7.87</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr"/>
+      <c r="T191" t="inlineStr"/>
       <c r="V191">
         <f>(I191-O191)^2+(J191-P191)^2+(K191-Q191)^2</f>
         <v/>
@@ -21491,22 +19797,11 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="T192" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U192" t="n">
-        <v>7.87</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr"/>
+      <c r="T192" t="inlineStr"/>
       <c r="V192">
         <f>(I192-O192)^2+(J192-P192)^2+(K192-Q192)^2</f>
         <v/>
@@ -21579,22 +19874,11 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="T193" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U193" t="n">
-        <v>7.87</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr"/>
+      <c r="T193" t="inlineStr"/>
       <c r="V193">
         <f>(I193-O193)^2+(J193-P193)^2+(K193-Q193)^2</f>
         <v/>
@@ -21667,22 +19951,11 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="T194" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U194" t="n">
-        <v>16.22</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr"/>
+      <c r="T194" t="inlineStr"/>
       <c r="V194">
         <f>(I194-O194)^2+(J194-P194)^2+(K194-Q194)^2</f>
         <v/>
@@ -21755,22 +20028,11 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="T195" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U195" t="n">
-        <v>16.22</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr"/>
+      <c r="T195" t="inlineStr"/>
       <c r="V195">
         <f>(I195-O195)^2+(J195-P195)^2+(K195-Q195)^2</f>
         <v/>
@@ -21843,22 +20105,11 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="T196" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U196" t="n">
-        <v>16.22</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr"/>
+      <c r="T196" t="inlineStr"/>
       <c r="V196">
         <f>(I196-O196)^2+(J196-P196)^2+(K196-Q196)^2</f>
         <v/>
@@ -21931,22 +20182,11 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="T197" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U197" t="n">
-        <v>16.22</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr"/>
+      <c r="T197" t="inlineStr"/>
       <c r="V197">
         <f>(I197-O197)^2+(J197-P197)^2+(K197-Q197)^2</f>
         <v/>
@@ -22371,22 +20611,11 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="T202" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U202" t="n">
-        <v>4.29</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr"/>
+      <c r="T202" t="inlineStr"/>
       <c r="V202">
         <f>(I202-O202)^2+(J202-P202)^2+(K202-Q202)^2</f>
         <v/>
@@ -22459,22 +20688,11 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="T203" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U203" t="n">
-        <v>4.29</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr"/>
+      <c r="T203" t="inlineStr"/>
       <c r="V203">
         <f>(I203-O203)^2+(J203-P203)^2+(K203-Q203)^2</f>
         <v/>
@@ -22547,22 +20765,11 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="T204" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U204" t="n">
-        <v>4.29</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr"/>
+      <c r="T204" t="inlineStr"/>
       <c r="V204">
         <f>(I204-O204)^2+(J204-P204)^2+(K204-Q204)^2</f>
         <v/>
@@ -22635,22 +20842,11 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="T205" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U205" t="n">
-        <v>4.29</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr"/>
+      <c r="T205" t="inlineStr"/>
       <c r="V205">
         <f>(I205-O205)^2+(J205-P205)^2+(K205-Q205)^2</f>
         <v/>
@@ -23075,22 +21271,11 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="T210" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U210" t="n">
-        <v>11.58</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr"/>
+      <c r="T210" t="inlineStr"/>
       <c r="V210">
         <f>(I210-O210)^2+(J210-P210)^2+(K210-Q210)^2</f>
         <v/>
@@ -23163,22 +21348,11 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="T211" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U211" t="n">
-        <v>11.58</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr"/>
+      <c r="T211" t="inlineStr"/>
       <c r="V211">
         <f>(I211-O211)^2+(J211-P211)^2+(K211-Q211)^2</f>
         <v/>
@@ -23251,22 +21425,11 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="T212" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U212" t="n">
-        <v>11.58</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr"/>
+      <c r="T212" t="inlineStr"/>
       <c r="V212">
         <f>(I212-O212)^2+(J212-P212)^2+(K212-Q212)^2</f>
         <v/>
@@ -23339,22 +21502,11 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="T213" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U213" t="n">
-        <v>11.58</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr"/>
+      <c r="T213" t="inlineStr"/>
       <c r="V213">
         <f>(I213-O213)^2+(J213-P213)^2+(K213-Q213)^2</f>
         <v/>
@@ -23427,22 +21579,11 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T214" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U214" t="n">
-        <v>10.26</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr"/>
+      <c r="T214" t="inlineStr"/>
       <c r="V214">
         <f>(I214-O214)^2+(J214-P214)^2+(K214-Q214)^2</f>
         <v/>
@@ -23515,22 +21656,11 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T215" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U215" t="n">
-        <v>10.26</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr"/>
+      <c r="T215" t="inlineStr"/>
       <c r="V215">
         <f>(I215-O215)^2+(J215-P215)^2+(K215-Q215)^2</f>
         <v/>
@@ -23603,22 +21733,11 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T216" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U216" t="n">
-        <v>10.26</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr"/>
+      <c r="T216" t="inlineStr"/>
       <c r="V216">
         <f>(I216-O216)^2+(J216-P216)^2+(K216-Q216)^2</f>
         <v/>
@@ -23691,22 +21810,11 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T217" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U217" t="n">
-        <v>10.26</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr"/>
+      <c r="T217" t="inlineStr"/>
       <c r="V217">
         <f>(I217-O217)^2+(J217-P217)^2+(K217-Q217)^2</f>
         <v/>
@@ -24131,22 +22239,11 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T222" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U222" t="n">
-        <v>5.29</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr"/>
+      <c r="T222" t="inlineStr"/>
       <c r="V222">
         <f>(I222-O222)^2+(J222-P222)^2+(K222-Q222)^2</f>
         <v/>
@@ -24219,22 +22316,11 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T223" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U223" t="n">
-        <v>5.29</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr"/>
+      <c r="T223" t="inlineStr"/>
       <c r="V223">
         <f>(I223-O223)^2+(J223-P223)^2+(K223-Q223)^2</f>
         <v/>
@@ -24307,22 +22393,11 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T224" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U224" t="n">
-        <v>5.29</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr"/>
+      <c r="T224" t="inlineStr"/>
       <c r="V224">
         <f>(I224-O224)^2+(J224-P224)^2+(K224-Q224)^2</f>
         <v/>
@@ -24395,22 +22470,11 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T225" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U225" t="n">
-        <v>5.29</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr"/>
+      <c r="T225" t="inlineStr"/>
       <c r="V225">
         <f>(I225-O225)^2+(J225-P225)^2+(K225-Q225)^2</f>
         <v/>
@@ -24483,22 +22547,11 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T226" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U226" t="n">
-        <v>9.609999999999999</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr"/>
+      <c r="T226" t="inlineStr"/>
       <c r="V226">
         <f>(I226-O226)^2+(J226-P226)^2+(K226-Q226)^2</f>
         <v/>
@@ -24571,22 +22624,11 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T227" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U227" t="n">
-        <v>9.609999999999999</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr"/>
+      <c r="T227" t="inlineStr"/>
       <c r="V227">
         <f>(I227-O227)^2+(J227-P227)^2+(K227-Q227)^2</f>
         <v/>
@@ -24659,22 +22701,11 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T228" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U228" t="n">
-        <v>9.609999999999999</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr"/>
+      <c r="T228" t="inlineStr"/>
       <c r="V228">
         <f>(I228-O228)^2+(J228-P228)^2+(K228-Q228)^2</f>
         <v/>
@@ -24747,22 +22778,11 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T229" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U229" t="n">
-        <v>9.609999999999999</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr"/>
+      <c r="T229" t="inlineStr"/>
       <c r="V229">
         <f>(I229-O229)^2+(J229-P229)^2+(K229-Q229)^2</f>
         <v/>
@@ -24835,22 +22855,11 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T230" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U230" t="n">
-        <v>7.08</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr"/>
+      <c r="T230" t="inlineStr"/>
       <c r="V230">
         <f>(I230-O230)^2+(J230-P230)^2+(K230-Q230)^2</f>
         <v/>
@@ -24923,22 +22932,11 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T231" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U231" t="n">
-        <v>7.08</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr"/>
+      <c r="T231" t="inlineStr"/>
       <c r="V231">
         <f>(I231-O231)^2+(J231-P231)^2+(K231-Q231)^2</f>
         <v/>
@@ -25011,22 +23009,11 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T232" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U232" t="n">
-        <v>7.08</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr"/>
+      <c r="T232" t="inlineStr"/>
       <c r="V232">
         <f>(I232-O232)^2+(J232-P232)^2+(K232-Q232)^2</f>
         <v/>
@@ -25099,22 +23086,11 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T233" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U233" t="n">
-        <v>7.08</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr"/>
+      <c r="T233" t="inlineStr"/>
       <c r="V233">
         <f>(I233-O233)^2+(J233-P233)^2+(K233-Q233)^2</f>
         <v/>
@@ -25187,22 +23163,11 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T234" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U234" t="n">
-        <v>12.48</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr"/>
+      <c r="T234" t="inlineStr"/>
       <c r="V234">
         <f>(I234-O234)^2+(J234-P234)^2+(K234-Q234)^2</f>
         <v/>
@@ -25275,22 +23240,11 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T235" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U235" t="n">
-        <v>12.48</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr"/>
+      <c r="T235" t="inlineStr"/>
       <c r="V235">
         <f>(I235-O235)^2+(J235-P235)^2+(K235-Q235)^2</f>
         <v/>
@@ -25363,22 +23317,11 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T236" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U236" t="n">
-        <v>12.48</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr"/>
+      <c r="T236" t="inlineStr"/>
       <c r="V236">
         <f>(I236-O236)^2+(J236-P236)^2+(K236-Q236)^2</f>
         <v/>
@@ -25451,22 +23394,11 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S237" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T237" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U237" t="n">
-        <v>12.48</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr"/>
+      <c r="T237" t="inlineStr"/>
       <c r="V237">
         <f>(I237-O237)^2+(J237-P237)^2+(K237-Q237)^2</f>
         <v/>
@@ -25539,22 +23471,11 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T238" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U238" t="n">
-        <v>3.61</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr"/>
+      <c r="T238" t="inlineStr"/>
       <c r="V238">
         <f>(I238-O238)^2+(J238-P238)^2+(K238-Q238)^2</f>
         <v/>
@@ -25627,22 +23548,11 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S239" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T239" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U239" t="n">
-        <v>3.61</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S239" t="inlineStr"/>
+      <c r="T239" t="inlineStr"/>
       <c r="V239">
         <f>(I239-O239)^2+(J239-P239)^2+(K239-Q239)^2</f>
         <v/>
@@ -25715,22 +23625,11 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T240" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U240" t="n">
-        <v>3.61</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr"/>
+      <c r="T240" t="inlineStr"/>
       <c r="V240">
         <f>(I240-O240)^2+(J240-P240)^2+(K240-Q240)^2</f>
         <v/>
@@ -25803,22 +23702,11 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T241" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U241" t="n">
-        <v>3.61</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr"/>
+      <c r="T241" t="inlineStr"/>
       <c r="V241">
         <f>(I241-O241)^2+(J241-P241)^2+(K241-Q241)^2</f>
         <v/>
@@ -25891,22 +23779,11 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T242" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U242" t="n">
-        <v>13.67</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr"/>
+      <c r="T242" t="inlineStr"/>
       <c r="V242">
         <f>(I242-O242)^2+(J242-P242)^2+(K242-Q242)^2</f>
         <v/>
@@ -25979,22 +23856,11 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T243" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U243" t="n">
-        <v>13.67</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr"/>
+      <c r="T243" t="inlineStr"/>
       <c r="V243">
         <f>(I243-O243)^2+(J243-P243)^2+(K243-Q243)^2</f>
         <v/>
@@ -26067,22 +23933,11 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T244" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U244" t="n">
-        <v>13.67</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr"/>
+      <c r="T244" t="inlineStr"/>
       <c r="V244">
         <f>(I244-O244)^2+(J244-P244)^2+(K244-Q244)^2</f>
         <v/>
@@ -26155,22 +24010,11 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T245" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U245" t="n">
-        <v>13.67</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr"/>
+      <c r="T245" t="inlineStr"/>
       <c r="V245">
         <f>(I245-O245)^2+(J245-P245)^2+(K245-Q245)^2</f>
         <v/>
@@ -26595,22 +24439,11 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="T250" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U250" t="n">
-        <v>8.5</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr"/>
+      <c r="T250" t="inlineStr"/>
       <c r="V250">
         <f>(I250-O250)^2+(J250-P250)^2+(K250-Q250)^2</f>
         <v/>
@@ -26683,22 +24516,11 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="T251" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U251" t="n">
-        <v>8.5</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr"/>
+      <c r="T251" t="inlineStr"/>
       <c r="V251">
         <f>(I251-O251)^2+(J251-P251)^2+(K251-Q251)^2</f>
         <v/>
@@ -26771,22 +24593,11 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="T252" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U252" t="n">
-        <v>8.5</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr"/>
+      <c r="T252" t="inlineStr"/>
       <c r="V252">
         <f>(I252-O252)^2+(J252-P252)^2+(K252-Q252)^2</f>
         <v/>
@@ -26859,22 +24670,11 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="T253" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U253" t="n">
-        <v>8.5</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr"/>
+      <c r="T253" t="inlineStr"/>
       <c r="V253">
         <f>(I253-O253)^2+(J253-P253)^2+(K253-Q253)^2</f>
         <v/>
@@ -26947,22 +24747,11 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T254" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U254" t="n">
-        <v>13.41</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr"/>
+      <c r="T254" t="inlineStr"/>
       <c r="V254">
         <f>(I254-O254)^2+(J254-P254)^2+(K254-Q254)^2</f>
         <v/>
@@ -27035,22 +24824,11 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S255" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T255" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U255" t="n">
-        <v>13.41</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr"/>
+      <c r="T255" t="inlineStr"/>
       <c r="V255">
         <f>(I255-O255)^2+(J255-P255)^2+(K255-Q255)^2</f>
         <v/>
@@ -27123,22 +24901,11 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T256" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U256" t="n">
-        <v>13.41</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr"/>
+      <c r="T256" t="inlineStr"/>
       <c r="V256">
         <f>(I256-O256)^2+(J256-P256)^2+(K256-Q256)^2</f>
         <v/>
@@ -27211,22 +24978,11 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T257" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U257" t="n">
-        <v>13.41</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr"/>
+      <c r="T257" t="inlineStr"/>
       <c r="V257">
         <f>(I257-O257)^2+(J257-P257)^2+(K257-Q257)^2</f>
         <v/>

--- a/desk_backtest.xlsx
+++ b/desk_backtest.xlsx
@@ -5211,11 +5211,22 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>9.31</v>
+      </c>
       <c r="V6">
         <f>(I6-O6)^2+(J6-P6)^2+(K6-Q6)^2</f>
         <v/>
@@ -5288,11 +5299,22 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>9.31</v>
+      </c>
       <c r="V7">
         <f>(I7-O7)^2+(J7-P7)^2+(K7-Q7)^2</f>
         <v/>
@@ -5365,11 +5387,22 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>9.31</v>
+      </c>
       <c r="V8">
         <f>(I8-O8)^2+(J8-P8)^2+(K8-Q8)^2</f>
         <v/>
@@ -5442,11 +5475,22 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>9.31</v>
+      </c>
       <c r="V9">
         <f>(I9-O9)^2+(J9-P9)^2+(K9-Q9)^2</f>
         <v/>
@@ -5519,11 +5563,22 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>16.73</v>
+      </c>
       <c r="V10">
         <f>(I10-O10)^2+(J10-P10)^2+(K10-Q10)^2</f>
         <v/>
@@ -5596,11 +5651,22 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>16.73</v>
+      </c>
       <c r="V11">
         <f>(I11-O11)^2+(J11-P11)^2+(K11-Q11)^2</f>
         <v/>
@@ -5673,11 +5739,22 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>16.73</v>
+      </c>
       <c r="V12">
         <f>(I12-O12)^2+(J12-P12)^2+(K12-Q12)^2</f>
         <v/>
@@ -5750,11 +5827,22 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>16.73</v>
+      </c>
       <c r="V13">
         <f>(I13-O13)^2+(J13-P13)^2+(K13-Q13)^2</f>
         <v/>
@@ -6135,11 +6223,22 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>3.83</v>
+      </c>
       <c r="V18">
         <f>(I18-O18)^2+(J18-P18)^2+(K18-Q18)^2</f>
         <v/>
@@ -6212,11 +6311,22 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>3.83</v>
+      </c>
       <c r="V19">
         <f>(I19-O19)^2+(J19-P19)^2+(K19-Q19)^2</f>
         <v/>
@@ -6289,11 +6399,22 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>3.83</v>
+      </c>
       <c r="V20">
         <f>(I20-O20)^2+(J20-P20)^2+(K20-Q20)^2</f>
         <v/>
@@ -6366,11 +6487,22 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>3.83</v>
+      </c>
       <c r="V21">
         <f>(I21-O21)^2+(J21-P21)^2+(K21-Q21)^2</f>
         <v/>
@@ -7059,11 +7191,22 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
+        <v>9.84</v>
+      </c>
       <c r="V30">
         <f>(I30-O30)^2+(J30-P30)^2+(K30-Q30)^2</f>
         <v/>
@@ -7136,11 +7279,22 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
+        <v>9.84</v>
+      </c>
       <c r="V31">
         <f>(I31-O31)^2+(J31-P31)^2+(K31-Q31)^2</f>
         <v/>
@@ -7213,11 +7367,22 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
+        <v>9.84</v>
+      </c>
       <c r="V32">
         <f>(I32-O32)^2+(J32-P32)^2+(K32-Q32)^2</f>
         <v/>
@@ -7290,11 +7455,22 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
+        <v>9.84</v>
+      </c>
       <c r="V33">
         <f>(I33-O33)^2+(J33-P33)^2+(K33-Q33)^2</f>
         <v/>
@@ -7367,11 +7543,22 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
+        <v>7.02</v>
+      </c>
       <c r="V34">
         <f>(I34-O34)^2+(J34-P34)^2+(K34-Q34)^2</f>
         <v/>
@@ -7444,11 +7631,22 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
+        <v>7.02</v>
+      </c>
       <c r="V35">
         <f>(I35-O35)^2+(J35-P35)^2+(K35-Q35)^2</f>
         <v/>
@@ -7521,11 +7719,22 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
+        <v>7.02</v>
+      </c>
       <c r="V36">
         <f>(I36-O36)^2+(J36-P36)^2+(K36-Q36)^2</f>
         <v/>
@@ -7598,11 +7807,22 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
+        <v>7.02</v>
+      </c>
       <c r="V37">
         <f>(I37-O37)^2+(J37-P37)^2+(K37-Q37)^2</f>
         <v/>
@@ -8379,11 +8599,22 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
+        <v>10.46</v>
+      </c>
       <c r="V46">
         <f>(I46-O46)^2+(J46-P46)^2+(K46-Q46)^2</f>
         <v/>
@@ -8456,11 +8687,22 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
+        <v>10.46</v>
+      </c>
       <c r="V47">
         <f>(I47-O47)^2+(J47-P47)^2+(K47-Q47)^2</f>
         <v/>
@@ -8533,11 +8775,22 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
+        <v>10.46</v>
+      </c>
       <c r="V48">
         <f>(I48-O48)^2+(J48-P48)^2+(K48-Q48)^2</f>
         <v/>
@@ -8610,11 +8863,22 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
+        <v>10.46</v>
+      </c>
       <c r="V49">
         <f>(I49-O49)^2+(J49-P49)^2+(K49-Q49)^2</f>
         <v/>
@@ -8995,11 +9259,22 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
+        <v>6.22</v>
+      </c>
       <c r="V54">
         <f>(I54-O54)^2+(J54-P54)^2+(K54-Q54)^2</f>
         <v/>
@@ -9072,11 +9347,22 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
+        <v>6.22</v>
+      </c>
       <c r="V55">
         <f>(I55-O55)^2+(J55-P55)^2+(K55-Q55)^2</f>
         <v/>
@@ -9149,11 +9435,22 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U56" t="n">
+        <v>6.22</v>
+      </c>
       <c r="V56">
         <f>(I56-O56)^2+(J56-P56)^2+(K56-Q56)^2</f>
         <v/>
@@ -9226,11 +9523,22 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U57" t="n">
+        <v>6.22</v>
+      </c>
       <c r="V57">
         <f>(I57-O57)^2+(J57-P57)^2+(K57-Q57)^2</f>
         <v/>
@@ -9303,11 +9611,22 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U58" t="n">
+        <v>12.89</v>
+      </c>
       <c r="V58">
         <f>(I58-O58)^2+(J58-P58)^2+(K58-Q58)^2</f>
         <v/>
@@ -9380,11 +9699,22 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U59" t="n">
+        <v>12.89</v>
+      </c>
       <c r="V59">
         <f>(I59-O59)^2+(J59-P59)^2+(K59-Q59)^2</f>
         <v/>
@@ -9457,11 +9787,22 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U60" t="n">
+        <v>12.89</v>
+      </c>
       <c r="V60">
         <f>(I60-O60)^2+(J60-P60)^2+(K60-Q60)^2</f>
         <v/>
@@ -9534,11 +9875,22 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
+        <v>12.89</v>
+      </c>
       <c r="V61">
         <f>(I61-O61)^2+(J61-P61)^2+(K61-Q61)^2</f>
         <v/>
@@ -9963,11 +10315,22 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U66" t="n">
+        <v>9.69</v>
+      </c>
       <c r="V66">
         <f>(I66-O66)^2+(J66-P66)^2+(K66-Q66)^2</f>
         <v/>
@@ -10040,11 +10403,22 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
+        <v>9.69</v>
+      </c>
       <c r="V67">
         <f>(I67-O67)^2+(J67-P67)^2+(K67-Q67)^2</f>
         <v/>
@@ -10117,11 +10491,22 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
+        <v>9.69</v>
+      </c>
       <c r="V68">
         <f>(I68-O68)^2+(J68-P68)^2+(K68-Q68)^2</f>
         <v/>
@@ -10194,11 +10579,22 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
+        <v>9.69</v>
+      </c>
       <c r="V69">
         <f>(I69-O69)^2+(J69-P69)^2+(K69-Q69)^2</f>
         <v/>
@@ -10579,11 +10975,22 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U74" t="n">
+        <v>6.49</v>
+      </c>
       <c r="V74">
         <f>(I74-O74)^2+(J74-P74)^2+(K74-Q74)^2</f>
         <v/>
@@ -10656,11 +11063,22 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U75" t="n">
+        <v>6.49</v>
+      </c>
       <c r="V75">
         <f>(I75-O75)^2+(J75-P75)^2+(K75-Q75)^2</f>
         <v/>
@@ -10733,11 +11151,22 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U76" t="n">
+        <v>6.49</v>
+      </c>
       <c r="V76">
         <f>(I76-O76)^2+(J76-P76)^2+(K76-Q76)^2</f>
         <v/>
@@ -10810,11 +11239,22 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U77" t="n">
+        <v>6.49</v>
+      </c>
       <c r="V77">
         <f>(I77-O77)^2+(J77-P77)^2+(K77-Q77)^2</f>
         <v/>
@@ -11195,11 +11635,22 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U82" t="n">
+        <v>6.7</v>
+      </c>
       <c r="V82">
         <f>(I82-O82)^2+(J82-P82)^2+(K82-Q82)^2</f>
         <v/>
@@ -11272,11 +11723,22 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U83" t="n">
+        <v>6.7</v>
+      </c>
       <c r="V83">
         <f>(I83-O83)^2+(J83-P83)^2+(K83-Q83)^2</f>
         <v/>
@@ -11349,11 +11811,22 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U84" t="n">
+        <v>6.7</v>
+      </c>
       <c r="V84">
         <f>(I84-O84)^2+(J84-P84)^2+(K84-Q84)^2</f>
         <v/>
@@ -11426,11 +11899,22 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U85" t="n">
+        <v>6.7</v>
+      </c>
       <c r="V85">
         <f>(I85-O85)^2+(J85-P85)^2+(K85-Q85)^2</f>
         <v/>
@@ -11503,11 +11987,22 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U86" t="n">
+        <v>9.94</v>
+      </c>
       <c r="V86">
         <f>(I86-O86)^2+(J86-P86)^2+(K86-Q86)^2</f>
         <v/>
@@ -11580,11 +12075,22 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U87" t="n">
+        <v>9.94</v>
+      </c>
       <c r="V87">
         <f>(I87-O87)^2+(J87-P87)^2+(K87-Q87)^2</f>
         <v/>
@@ -11657,11 +12163,22 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U88" t="n">
+        <v>9.94</v>
+      </c>
       <c r="V88">
         <f>(I88-O88)^2+(J88-P88)^2+(K88-Q88)^2</f>
         <v/>
@@ -11734,11 +12251,22 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U89" t="n">
+        <v>9.94</v>
+      </c>
       <c r="V89">
         <f>(I89-O89)^2+(J89-P89)^2+(K89-Q89)^2</f>
         <v/>
@@ -11811,11 +12339,22 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U90" t="n">
+        <v>8.44</v>
+      </c>
       <c r="V90">
         <f>(I90-O90)^2+(J90-P90)^2+(K90-Q90)^2</f>
         <v/>
@@ -11888,11 +12427,22 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U91" t="n">
+        <v>8.44</v>
+      </c>
       <c r="V91">
         <f>(I91-O91)^2+(J91-P91)^2+(K91-Q91)^2</f>
         <v/>
@@ -11965,11 +12515,22 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U92" t="n">
+        <v>8.44</v>
+      </c>
       <c r="V92">
         <f>(I92-O92)^2+(J92-P92)^2+(K92-Q92)^2</f>
         <v/>
@@ -12042,11 +12603,22 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U93" t="n">
+        <v>8.44</v>
+      </c>
       <c r="V93">
         <f>(I93-O93)^2+(J93-P93)^2+(K93-Q93)^2</f>
         <v/>
@@ -12119,11 +12691,22 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U94" t="n">
+        <v>8.550000000000001</v>
+      </c>
       <c r="V94">
         <f>(I94-O94)^2+(J94-P94)^2+(K94-Q94)^2</f>
         <v/>
@@ -12196,11 +12779,22 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U95" t="n">
+        <v>8.550000000000001</v>
+      </c>
       <c r="V95">
         <f>(I95-O95)^2+(J95-P95)^2+(K95-Q95)^2</f>
         <v/>
@@ -12273,11 +12867,22 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U96" t="n">
+        <v>8.550000000000001</v>
+      </c>
       <c r="V96">
         <f>(I96-O96)^2+(J96-P96)^2+(K96-Q96)^2</f>
         <v/>
@@ -12350,11 +12955,22 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U97" t="n">
+        <v>8.550000000000001</v>
+      </c>
       <c r="V97">
         <f>(I97-O97)^2+(J97-P97)^2+(K97-Q97)^2</f>
         <v/>
@@ -12427,11 +13043,22 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U98" t="n">
+        <v>9.84</v>
+      </c>
       <c r="V98">
         <f>(I98-O98)^2+(J98-P98)^2+(K98-Q98)^2</f>
         <v/>
@@ -12504,11 +13131,22 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U99" t="n">
+        <v>9.84</v>
+      </c>
       <c r="V99">
         <f>(I99-O99)^2+(J99-P99)^2+(K99-Q99)^2</f>
         <v/>
@@ -12581,11 +13219,22 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U100" t="n">
+        <v>9.84</v>
+      </c>
       <c r="V100">
         <f>(I100-O100)^2+(J100-P100)^2+(K100-Q100)^2</f>
         <v/>
@@ -12658,11 +13307,22 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S101" t="inlineStr"/>
-      <c r="T101" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U101" t="n">
+        <v>9.84</v>
+      </c>
       <c r="V101">
         <f>(I101-O101)^2+(J101-P101)^2+(K101-Q101)^2</f>
         <v/>
@@ -12735,11 +13395,22 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr"/>
-      <c r="T102" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U102" t="n">
+        <v>10.36</v>
+      </c>
       <c r="V102">
         <f>(I102-O102)^2+(J102-P102)^2+(K102-Q102)^2</f>
         <v/>
@@ -12812,11 +13483,22 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr"/>
-      <c r="T103" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U103" t="n">
+        <v>10.36</v>
+      </c>
       <c r="V103">
         <f>(I103-O103)^2+(J103-P103)^2+(K103-Q103)^2</f>
         <v/>
@@ -12889,11 +13571,22 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U104" t="n">
+        <v>10.36</v>
+      </c>
       <c r="V104">
         <f>(I104-O104)^2+(J104-P104)^2+(K104-Q104)^2</f>
         <v/>
@@ -12966,11 +13659,22 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U105" t="n">
+        <v>10.36</v>
+      </c>
       <c r="V105">
         <f>(I105-O105)^2+(J105-P105)^2+(K105-Q105)^2</f>
         <v/>
@@ -13351,11 +14055,22 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U110" t="n">
+        <v>13.58</v>
+      </c>
       <c r="V110">
         <f>(I110-O110)^2+(J110-P110)^2+(K110-Q110)^2</f>
         <v/>
@@ -13428,11 +14143,22 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S111" t="inlineStr"/>
-      <c r="T111" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U111" t="n">
+        <v>13.58</v>
+      </c>
       <c r="V111">
         <f>(I111-O111)^2+(J111-P111)^2+(K111-Q111)^2</f>
         <v/>
@@ -13505,11 +14231,22 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S112" t="inlineStr"/>
-      <c r="T112" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U112" t="n">
+        <v>13.58</v>
+      </c>
       <c r="V112">
         <f>(I112-O112)^2+(J112-P112)^2+(K112-Q112)^2</f>
         <v/>
@@ -13582,11 +14319,22 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S113" t="inlineStr"/>
-      <c r="T113" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U113" t="n">
+        <v>13.58</v>
+      </c>
       <c r="V113">
         <f>(I113-O113)^2+(J113-P113)^2+(K113-Q113)^2</f>
         <v/>
@@ -13659,11 +14407,22 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S114" t="inlineStr"/>
-      <c r="T114" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U114" t="n">
+        <v>5.39</v>
+      </c>
       <c r="V114">
         <f>(I114-O114)^2+(J114-P114)^2+(K114-Q114)^2</f>
         <v/>
@@ -13736,11 +14495,22 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S115" t="inlineStr"/>
-      <c r="T115" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U115" t="n">
+        <v>5.39</v>
+      </c>
       <c r="V115">
         <f>(I115-O115)^2+(J115-P115)^2+(K115-Q115)^2</f>
         <v/>
@@ -13813,11 +14583,22 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S116" t="inlineStr"/>
-      <c r="T116" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U116" t="n">
+        <v>5.39</v>
+      </c>
       <c r="V116">
         <f>(I116-O116)^2+(J116-P116)^2+(K116-Q116)^2</f>
         <v/>
@@ -13890,11 +14671,22 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U117" t="n">
+        <v>5.39</v>
+      </c>
       <c r="V117">
         <f>(I117-O117)^2+(J117-P117)^2+(K117-Q117)^2</f>
         <v/>
@@ -14275,11 +15067,22 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S122" t="inlineStr"/>
-      <c r="T122" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U122" t="n">
+        <v>11.17</v>
+      </c>
       <c r="V122">
         <f>(I122-O122)^2+(J122-P122)^2+(K122-Q122)^2</f>
         <v/>
@@ -14352,11 +15155,22 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S123" t="inlineStr"/>
-      <c r="T123" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U123" t="n">
+        <v>11.17</v>
+      </c>
       <c r="V123">
         <f>(I123-O123)^2+(J123-P123)^2+(K123-Q123)^2</f>
         <v/>
@@ -14429,11 +15243,22 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S124" t="inlineStr"/>
-      <c r="T124" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U124" t="n">
+        <v>11.17</v>
+      </c>
       <c r="V124">
         <f>(I124-O124)^2+(J124-P124)^2+(K124-Q124)^2</f>
         <v/>
@@ -14506,11 +15331,22 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S125" t="inlineStr"/>
-      <c r="T125" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U125" t="n">
+        <v>11.17</v>
+      </c>
       <c r="V125">
         <f>(I125-O125)^2+(J125-P125)^2+(K125-Q125)^2</f>
         <v/>
@@ -14583,11 +15419,22 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S126" t="inlineStr"/>
-      <c r="T126" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U126" t="n">
+        <v>9.609999999999999</v>
+      </c>
       <c r="V126">
         <f>(I126-O126)^2+(J126-P126)^2+(K126-Q126)^2</f>
         <v/>
@@ -14660,11 +15507,22 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S127" t="inlineStr"/>
-      <c r="T127" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U127" t="n">
+        <v>9.609999999999999</v>
+      </c>
       <c r="V127">
         <f>(I127-O127)^2+(J127-P127)^2+(K127-Q127)^2</f>
         <v/>
@@ -14737,11 +15595,22 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S128" t="inlineStr"/>
-      <c r="T128" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U128" t="n">
+        <v>9.609999999999999</v>
+      </c>
       <c r="V128">
         <f>(I128-O128)^2+(J128-P128)^2+(K128-Q128)^2</f>
         <v/>
@@ -14814,11 +15683,22 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S129" t="inlineStr"/>
-      <c r="T129" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U129" t="n">
+        <v>9.609999999999999</v>
+      </c>
       <c r="V129">
         <f>(I129-O129)^2+(J129-P129)^2+(K129-Q129)^2</f>
         <v/>
@@ -15243,11 +16123,22 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S134" t="inlineStr"/>
-      <c r="T134" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U134" t="n">
+        <v>9.210000000000001</v>
+      </c>
       <c r="V134">
         <f>(I134-O134)^2+(J134-P134)^2+(K134-Q134)^2</f>
         <v/>
@@ -15320,11 +16211,22 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S135" t="inlineStr"/>
-      <c r="T135" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U135" t="n">
+        <v>9.210000000000001</v>
+      </c>
       <c r="V135">
         <f>(I135-O135)^2+(J135-P135)^2+(K135-Q135)^2</f>
         <v/>
@@ -15397,11 +16299,22 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr"/>
-      <c r="T136" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U136" t="n">
+        <v>9.210000000000001</v>
+      </c>
       <c r="V136">
         <f>(I136-O136)^2+(J136-P136)^2+(K136-Q136)^2</f>
         <v/>
@@ -15474,11 +16387,22 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S137" t="inlineStr"/>
-      <c r="T137" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U137" t="n">
+        <v>9.210000000000001</v>
+      </c>
       <c r="V137">
         <f>(I137-O137)^2+(J137-P137)^2+(K137-Q137)^2</f>
         <v/>
@@ -16211,11 +17135,22 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S146" t="inlineStr"/>
-      <c r="T146" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U146" t="n">
+        <v>12.34</v>
+      </c>
       <c r="V146">
         <f>(I146-O146)^2+(J146-P146)^2+(K146-Q146)^2</f>
         <v/>
@@ -16288,11 +17223,22 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S147" t="inlineStr"/>
-      <c r="T147" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U147" t="n">
+        <v>12.34</v>
+      </c>
       <c r="V147">
         <f>(I147-O147)^2+(J147-P147)^2+(K147-Q147)^2</f>
         <v/>
@@ -16365,11 +17311,22 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S148" t="inlineStr"/>
-      <c r="T148" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U148" t="n">
+        <v>12.34</v>
+      </c>
       <c r="V148">
         <f>(I148-O148)^2+(J148-P148)^2+(K148-Q148)^2</f>
         <v/>
@@ -16442,11 +17399,22 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S149" t="inlineStr"/>
-      <c r="T149" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U149" t="n">
+        <v>12.34</v>
+      </c>
       <c r="V149">
         <f>(I149-O149)^2+(J149-P149)^2+(K149-Q149)^2</f>
         <v/>
@@ -16519,11 +17487,22 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S150" t="inlineStr"/>
-      <c r="T150" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U150" t="n">
+        <v>9.640000000000001</v>
+      </c>
       <c r="V150">
         <f>(I150-O150)^2+(J150-P150)^2+(K150-Q150)^2</f>
         <v/>
@@ -16596,11 +17575,22 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S151" t="inlineStr"/>
-      <c r="T151" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U151" t="n">
+        <v>9.640000000000001</v>
+      </c>
       <c r="V151">
         <f>(I151-O151)^2+(J151-P151)^2+(K151-Q151)^2</f>
         <v/>
@@ -16673,11 +17663,22 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S152" t="inlineStr"/>
-      <c r="T152" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U152" t="n">
+        <v>9.640000000000001</v>
+      </c>
       <c r="V152">
         <f>(I152-O152)^2+(J152-P152)^2+(K152-Q152)^2</f>
         <v/>
@@ -16750,11 +17751,22 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S153" t="inlineStr"/>
-      <c r="T153" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U153" t="n">
+        <v>9.640000000000001</v>
+      </c>
       <c r="V153">
         <f>(I153-O153)^2+(J153-P153)^2+(K153-Q153)^2</f>
         <v/>
@@ -17135,11 +18147,22 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S158" t="inlineStr"/>
-      <c r="T158" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U158" t="n">
+        <v>11.86</v>
+      </c>
       <c r="V158">
         <f>(I158-O158)^2+(J158-P158)^2+(K158-Q158)^2</f>
         <v/>
@@ -17212,11 +18235,22 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S159" t="inlineStr"/>
-      <c r="T159" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U159" t="n">
+        <v>11.86</v>
+      </c>
       <c r="V159">
         <f>(I159-O159)^2+(J159-P159)^2+(K159-Q159)^2</f>
         <v/>
@@ -17289,11 +18323,22 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S160" t="inlineStr"/>
-      <c r="T160" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U160" t="n">
+        <v>11.86</v>
+      </c>
       <c r="V160">
         <f>(I160-O160)^2+(J160-P160)^2+(K160-Q160)^2</f>
         <v/>
@@ -17366,11 +18411,22 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S161" t="inlineStr"/>
-      <c r="T161" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U161" t="n">
+        <v>11.86</v>
+      </c>
       <c r="V161">
         <f>(I161-O161)^2+(J161-P161)^2+(K161-Q161)^2</f>
         <v/>
@@ -17443,11 +18499,22 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S162" t="inlineStr"/>
-      <c r="T162" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U162" t="n">
+        <v>7.66</v>
+      </c>
       <c r="V162">
         <f>(I162-O162)^2+(J162-P162)^2+(K162-Q162)^2</f>
         <v/>
@@ -17520,11 +18587,22 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S163" t="inlineStr"/>
-      <c r="T163" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U163" t="n">
+        <v>7.66</v>
+      </c>
       <c r="V163">
         <f>(I163-O163)^2+(J163-P163)^2+(K163-Q163)^2</f>
         <v/>
@@ -17597,11 +18675,22 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S164" t="inlineStr"/>
-      <c r="T164" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U164" t="n">
+        <v>7.66</v>
+      </c>
       <c r="V164">
         <f>(I164-O164)^2+(J164-P164)^2+(K164-Q164)^2</f>
         <v/>
@@ -17674,11 +18763,22 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S165" t="inlineStr"/>
-      <c r="T165" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U165" t="n">
+        <v>7.66</v>
+      </c>
       <c r="V165">
         <f>(I165-O165)^2+(J165-P165)^2+(K165-Q165)^2</f>
         <v/>
@@ -17751,11 +18851,22 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S166" t="inlineStr"/>
-      <c r="T166" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U166" t="n">
+        <v>7.96</v>
+      </c>
       <c r="V166">
         <f>(I166-O166)^2+(J166-P166)^2+(K166-Q166)^2</f>
         <v/>
@@ -17828,11 +18939,22 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S167" t="inlineStr"/>
-      <c r="T167" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U167" t="n">
+        <v>7.96</v>
+      </c>
       <c r="V167">
         <f>(I167-O167)^2+(J167-P167)^2+(K167-Q167)^2</f>
         <v/>
@@ -17905,11 +19027,22 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S168" t="inlineStr"/>
-      <c r="T168" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U168" t="n">
+        <v>7.96</v>
+      </c>
       <c r="V168">
         <f>(I168-O168)^2+(J168-P168)^2+(K168-Q168)^2</f>
         <v/>
@@ -17982,11 +19115,22 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S169" t="inlineStr"/>
-      <c r="T169" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U169" t="n">
+        <v>7.96</v>
+      </c>
       <c r="V169">
         <f>(I169-O169)^2+(J169-P169)^2+(K169-Q169)^2</f>
         <v/>
@@ -18719,11 +19863,22 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S178" t="inlineStr"/>
-      <c r="T178" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U178" t="n">
+        <v>14.24</v>
+      </c>
       <c r="V178">
         <f>(I178-O178)^2+(J178-P178)^2+(K178-Q178)^2</f>
         <v/>
@@ -18796,11 +19951,22 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S179" t="inlineStr"/>
-      <c r="T179" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U179" t="n">
+        <v>14.24</v>
+      </c>
       <c r="V179">
         <f>(I179-O179)^2+(J179-P179)^2+(K179-Q179)^2</f>
         <v/>
@@ -18873,11 +20039,22 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S180" t="inlineStr"/>
-      <c r="T180" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U180" t="n">
+        <v>14.24</v>
+      </c>
       <c r="V180">
         <f>(I180-O180)^2+(J180-P180)^2+(K180-Q180)^2</f>
         <v/>
@@ -18950,11 +20127,22 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S181" t="inlineStr"/>
-      <c r="T181" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U181" t="n">
+        <v>14.24</v>
+      </c>
       <c r="V181">
         <f>(I181-O181)^2+(J181-P181)^2+(K181-Q181)^2</f>
         <v/>
@@ -19027,11 +20215,22 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S182" t="inlineStr"/>
-      <c r="T182" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U182" t="n">
+        <v>11.26</v>
+      </c>
       <c r="V182">
         <f>(I182-O182)^2+(J182-P182)^2+(K182-Q182)^2</f>
         <v/>
@@ -19104,11 +20303,22 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S183" t="inlineStr"/>
-      <c r="T183" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U183" t="n">
+        <v>11.26</v>
+      </c>
       <c r="V183">
         <f>(I183-O183)^2+(J183-P183)^2+(K183-Q183)^2</f>
         <v/>
@@ -19181,11 +20391,22 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S184" t="inlineStr"/>
-      <c r="T184" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U184" t="n">
+        <v>11.26</v>
+      </c>
       <c r="V184">
         <f>(I184-O184)^2+(J184-P184)^2+(K184-Q184)^2</f>
         <v/>
@@ -19258,11 +20479,22 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S185" t="inlineStr"/>
-      <c r="T185" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U185" t="n">
+        <v>11.26</v>
+      </c>
       <c r="V185">
         <f>(I185-O185)^2+(J185-P185)^2+(K185-Q185)^2</f>
         <v/>
@@ -19335,11 +20567,22 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S186" t="inlineStr"/>
-      <c r="T186" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U186" t="n">
+        <v>7.72</v>
+      </c>
       <c r="V186">
         <f>(I186-O186)^2+(J186-P186)^2+(K186-Q186)^2</f>
         <v/>
@@ -19412,11 +20655,22 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S187" t="inlineStr"/>
-      <c r="T187" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U187" t="n">
+        <v>7.72</v>
+      </c>
       <c r="V187">
         <f>(I187-O187)^2+(J187-P187)^2+(K187-Q187)^2</f>
         <v/>
@@ -19489,11 +20743,22 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S188" t="inlineStr"/>
-      <c r="T188" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U188" t="n">
+        <v>7.72</v>
+      </c>
       <c r="V188">
         <f>(I188-O188)^2+(J188-P188)^2+(K188-Q188)^2</f>
         <v/>
@@ -19566,11 +20831,22 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S189" t="inlineStr"/>
-      <c r="T189" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U189" t="n">
+        <v>7.72</v>
+      </c>
       <c r="V189">
         <f>(I189-O189)^2+(J189-P189)^2+(K189-Q189)^2</f>
         <v/>
@@ -19643,11 +20919,22 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S190" t="inlineStr"/>
-      <c r="T190" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U190" t="n">
+        <v>7.87</v>
+      </c>
       <c r="V190">
         <f>(I190-O190)^2+(J190-P190)^2+(K190-Q190)^2</f>
         <v/>
@@ -19720,11 +21007,22 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S191" t="inlineStr"/>
-      <c r="T191" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U191" t="n">
+        <v>7.87</v>
+      </c>
       <c r="V191">
         <f>(I191-O191)^2+(J191-P191)^2+(K191-Q191)^2</f>
         <v/>
@@ -19797,11 +21095,22 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S192" t="inlineStr"/>
-      <c r="T192" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U192" t="n">
+        <v>7.87</v>
+      </c>
       <c r="V192">
         <f>(I192-O192)^2+(J192-P192)^2+(K192-Q192)^2</f>
         <v/>
@@ -19874,11 +21183,22 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S193" t="inlineStr"/>
-      <c r="T193" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U193" t="n">
+        <v>7.87</v>
+      </c>
       <c r="V193">
         <f>(I193-O193)^2+(J193-P193)^2+(K193-Q193)^2</f>
         <v/>
@@ -19951,11 +21271,22 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S194" t="inlineStr"/>
-      <c r="T194" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U194" t="n">
+        <v>16.22</v>
+      </c>
       <c r="V194">
         <f>(I194-O194)^2+(J194-P194)^2+(K194-Q194)^2</f>
         <v/>
@@ -20028,11 +21359,22 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S195" t="inlineStr"/>
-      <c r="T195" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U195" t="n">
+        <v>16.22</v>
+      </c>
       <c r="V195">
         <f>(I195-O195)^2+(J195-P195)^2+(K195-Q195)^2</f>
         <v/>
@@ -20105,11 +21447,22 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S196" t="inlineStr"/>
-      <c r="T196" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U196" t="n">
+        <v>16.22</v>
+      </c>
       <c r="V196">
         <f>(I196-O196)^2+(J196-P196)^2+(K196-Q196)^2</f>
         <v/>
@@ -20182,11 +21535,22 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S197" t="inlineStr"/>
-      <c r="T197" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U197" t="n">
+        <v>16.22</v>
+      </c>
       <c r="V197">
         <f>(I197-O197)^2+(J197-P197)^2+(K197-Q197)^2</f>
         <v/>
@@ -21271,11 +22635,22 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S210" t="inlineStr"/>
-      <c r="T210" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U210" t="n">
+        <v>11.58</v>
+      </c>
       <c r="V210">
         <f>(I210-O210)^2+(J210-P210)^2+(K210-Q210)^2</f>
         <v/>
@@ -21348,11 +22723,22 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S211" t="inlineStr"/>
-      <c r="T211" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U211" t="n">
+        <v>11.58</v>
+      </c>
       <c r="V211">
         <f>(I211-O211)^2+(J211-P211)^2+(K211-Q211)^2</f>
         <v/>
@@ -21425,11 +22811,22 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S212" t="inlineStr"/>
-      <c r="T212" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U212" t="n">
+        <v>11.58</v>
+      </c>
       <c r="V212">
         <f>(I212-O212)^2+(J212-P212)^2+(K212-Q212)^2</f>
         <v/>
@@ -21502,11 +22899,22 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S213" t="inlineStr"/>
-      <c r="T213" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U213" t="n">
+        <v>11.58</v>
+      </c>
       <c r="V213">
         <f>(I213-O213)^2+(J213-P213)^2+(K213-Q213)^2</f>
         <v/>
@@ -21579,11 +22987,22 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S214" t="inlineStr"/>
-      <c r="T214" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U214" t="n">
+        <v>10.26</v>
+      </c>
       <c r="V214">
         <f>(I214-O214)^2+(J214-P214)^2+(K214-Q214)^2</f>
         <v/>
@@ -21656,11 +23075,22 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S215" t="inlineStr"/>
-      <c r="T215" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U215" t="n">
+        <v>10.26</v>
+      </c>
       <c r="V215">
         <f>(I215-O215)^2+(J215-P215)^2+(K215-Q215)^2</f>
         <v/>
@@ -21733,11 +23163,22 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S216" t="inlineStr"/>
-      <c r="T216" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U216" t="n">
+        <v>10.26</v>
+      </c>
       <c r="V216">
         <f>(I216-O216)^2+(J216-P216)^2+(K216-Q216)^2</f>
         <v/>
@@ -21810,11 +23251,22 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S217" t="inlineStr"/>
-      <c r="T217" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U217" t="n">
+        <v>10.26</v>
+      </c>
       <c r="V217">
         <f>(I217-O217)^2+(J217-P217)^2+(K217-Q217)^2</f>
         <v/>
@@ -22547,11 +23999,22 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S226" t="inlineStr"/>
-      <c r="T226" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U226" t="n">
+        <v>9.609999999999999</v>
+      </c>
       <c r="V226">
         <f>(I226-O226)^2+(J226-P226)^2+(K226-Q226)^2</f>
         <v/>
@@ -22624,11 +24087,22 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S227" t="inlineStr"/>
-      <c r="T227" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U227" t="n">
+        <v>9.609999999999999</v>
+      </c>
       <c r="V227">
         <f>(I227-O227)^2+(J227-P227)^2+(K227-Q227)^2</f>
         <v/>
@@ -22701,11 +24175,22 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S228" t="inlineStr"/>
-      <c r="T228" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U228" t="n">
+        <v>9.609999999999999</v>
+      </c>
       <c r="V228">
         <f>(I228-O228)^2+(J228-P228)^2+(K228-Q228)^2</f>
         <v/>
@@ -22778,11 +24263,22 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S229" t="inlineStr"/>
-      <c r="T229" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U229" t="n">
+        <v>9.609999999999999</v>
+      </c>
       <c r="V229">
         <f>(I229-O229)^2+(J229-P229)^2+(K229-Q229)^2</f>
         <v/>
@@ -22855,11 +24351,22 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S230" t="inlineStr"/>
-      <c r="T230" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U230" t="n">
+        <v>7.08</v>
+      </c>
       <c r="V230">
         <f>(I230-O230)^2+(J230-P230)^2+(K230-Q230)^2</f>
         <v/>
@@ -22932,11 +24439,22 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S231" t="inlineStr"/>
-      <c r="T231" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U231" t="n">
+        <v>7.08</v>
+      </c>
       <c r="V231">
         <f>(I231-O231)^2+(J231-P231)^2+(K231-Q231)^2</f>
         <v/>
@@ -23009,11 +24527,22 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S232" t="inlineStr"/>
-      <c r="T232" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U232" t="n">
+        <v>7.08</v>
+      </c>
       <c r="V232">
         <f>(I232-O232)^2+(J232-P232)^2+(K232-Q232)^2</f>
         <v/>
@@ -23086,11 +24615,22 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S233" t="inlineStr"/>
-      <c r="T233" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U233" t="n">
+        <v>7.08</v>
+      </c>
       <c r="V233">
         <f>(I233-O233)^2+(J233-P233)^2+(K233-Q233)^2</f>
         <v/>
@@ -23163,11 +24703,22 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S234" t="inlineStr"/>
-      <c r="T234" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U234" t="n">
+        <v>12.48</v>
+      </c>
       <c r="V234">
         <f>(I234-O234)^2+(J234-P234)^2+(K234-Q234)^2</f>
         <v/>
@@ -23240,11 +24791,22 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S235" t="inlineStr"/>
-      <c r="T235" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U235" t="n">
+        <v>12.48</v>
+      </c>
       <c r="V235">
         <f>(I235-O235)^2+(J235-P235)^2+(K235-Q235)^2</f>
         <v/>
@@ -23317,11 +24879,22 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S236" t="inlineStr"/>
-      <c r="T236" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U236" t="n">
+        <v>12.48</v>
+      </c>
       <c r="V236">
         <f>(I236-O236)^2+(J236-P236)^2+(K236-Q236)^2</f>
         <v/>
@@ -23394,11 +24967,22 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S237" t="inlineStr"/>
-      <c r="T237" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U237" t="n">
+        <v>12.48</v>
+      </c>
       <c r="V237">
         <f>(I237-O237)^2+(J237-P237)^2+(K237-Q237)^2</f>
         <v/>
@@ -23779,11 +25363,22 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S242" t="inlineStr"/>
-      <c r="T242" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U242" t="n">
+        <v>13.67</v>
+      </c>
       <c r="V242">
         <f>(I242-O242)^2+(J242-P242)^2+(K242-Q242)^2</f>
         <v/>
@@ -23856,11 +25451,22 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S243" t="inlineStr"/>
-      <c r="T243" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U243" t="n">
+        <v>13.67</v>
+      </c>
       <c r="V243">
         <f>(I243-O243)^2+(J243-P243)^2+(K243-Q243)^2</f>
         <v/>
@@ -23933,11 +25539,22 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S244" t="inlineStr"/>
-      <c r="T244" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U244" t="n">
+        <v>13.67</v>
+      </c>
       <c r="V244">
         <f>(I244-O244)^2+(J244-P244)^2+(K244-Q244)^2</f>
         <v/>
@@ -24010,11 +25627,22 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S245" t="inlineStr"/>
-      <c r="T245" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U245" t="n">
+        <v>13.67</v>
+      </c>
       <c r="V245">
         <f>(I245-O245)^2+(J245-P245)^2+(K245-Q245)^2</f>
         <v/>
@@ -24439,11 +26067,22 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S250" t="inlineStr"/>
-      <c r="T250" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U250" t="n">
+        <v>8.5</v>
+      </c>
       <c r="V250">
         <f>(I250-O250)^2+(J250-P250)^2+(K250-Q250)^2</f>
         <v/>
@@ -24516,11 +26155,22 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S251" t="inlineStr"/>
-      <c r="T251" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U251" t="n">
+        <v>8.5</v>
+      </c>
       <c r="V251">
         <f>(I251-O251)^2+(J251-P251)^2+(K251-Q251)^2</f>
         <v/>
@@ -24593,11 +26243,22 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S252" t="inlineStr"/>
-      <c r="T252" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U252" t="n">
+        <v>8.5</v>
+      </c>
       <c r="V252">
         <f>(I252-O252)^2+(J252-P252)^2+(K252-Q252)^2</f>
         <v/>
@@ -24670,11 +26331,22 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S253" t="inlineStr"/>
-      <c r="T253" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U253" t="n">
+        <v>8.5</v>
+      </c>
       <c r="V253">
         <f>(I253-O253)^2+(J253-P253)^2+(K253-Q253)^2</f>
         <v/>
@@ -24747,11 +26419,22 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S254" t="inlineStr"/>
-      <c r="T254" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U254" t="n">
+        <v>13.41</v>
+      </c>
       <c r="V254">
         <f>(I254-O254)^2+(J254-P254)^2+(K254-Q254)^2</f>
         <v/>
@@ -24824,11 +26507,22 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S255" t="inlineStr"/>
-      <c r="T255" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U255" t="n">
+        <v>13.41</v>
+      </c>
       <c r="V255">
         <f>(I255-O255)^2+(J255-P255)^2+(K255-Q255)^2</f>
         <v/>
@@ -24901,11 +26595,22 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S256" t="inlineStr"/>
-      <c r="T256" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U256" t="n">
+        <v>13.41</v>
+      </c>
       <c r="V256">
         <f>(I256-O256)^2+(J256-P256)^2+(K256-Q256)^2</f>
         <v/>
@@ -24978,11 +26683,22 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="S257" t="inlineStr"/>
-      <c r="T257" t="inlineStr"/>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="U257" t="n">
+        <v>13.41</v>
+      </c>
       <c r="V257">
         <f>(I257-O257)^2+(J257-P257)^2+(K257-Q257)^2</f>
         <v/>

--- a/desk_backtest.xlsx
+++ b/desk_backtest.xlsx
@@ -6223,22 +6223,11 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U18" t="n">
-        <v>3.83</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
       <c r="V18">
         <f>(I18-O18)^2+(J18-P18)^2+(K18-Q18)^2</f>
         <v/>
@@ -6311,22 +6300,11 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U19" t="n">
-        <v>3.83</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
       <c r="V19">
         <f>(I19-O19)^2+(J19-P19)^2+(K19-Q19)^2</f>
         <v/>
@@ -6399,22 +6377,11 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U20" t="n">
-        <v>3.83</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
       <c r="V20">
         <f>(I20-O20)^2+(J20-P20)^2+(K20-Q20)^2</f>
         <v/>
@@ -6487,22 +6454,11 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U21" t="n">
-        <v>3.83</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
       <c r="V21">
         <f>(I21-O21)^2+(J21-P21)^2+(K21-Q21)^2</f>
         <v/>
@@ -7543,22 +7499,11 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U34" t="n">
-        <v>7.02</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
       <c r="V34">
         <f>(I34-O34)^2+(J34-P34)^2+(K34-Q34)^2</f>
         <v/>
@@ -7631,22 +7576,11 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U35" t="n">
-        <v>7.02</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
       <c r="V35">
         <f>(I35-O35)^2+(J35-P35)^2+(K35-Q35)^2</f>
         <v/>
@@ -7719,22 +7653,11 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U36" t="n">
-        <v>7.02</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
       <c r="V36">
         <f>(I36-O36)^2+(J36-P36)^2+(K36-Q36)^2</f>
         <v/>
@@ -7807,22 +7730,11 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U37" t="n">
-        <v>7.02</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
       <c r="V37">
         <f>(I37-O37)^2+(J37-P37)^2+(K37-Q37)^2</f>
         <v/>
@@ -9259,22 +9171,11 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U54" t="n">
-        <v>6.22</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
       <c r="V54">
         <f>(I54-O54)^2+(J54-P54)^2+(K54-Q54)^2</f>
         <v/>
@@ -9347,22 +9248,11 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U55" t="n">
-        <v>6.22</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
       <c r="V55">
         <f>(I55-O55)^2+(J55-P55)^2+(K55-Q55)^2</f>
         <v/>
@@ -9435,22 +9325,11 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U56" t="n">
-        <v>6.22</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
       <c r="V56">
         <f>(I56-O56)^2+(J56-P56)^2+(K56-Q56)^2</f>
         <v/>
@@ -9523,22 +9402,11 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U57" t="n">
-        <v>6.22</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
       <c r="V57">
         <f>(I57-O57)^2+(J57-P57)^2+(K57-Q57)^2</f>
         <v/>
@@ -10975,22 +10843,11 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U74" t="n">
-        <v>6.49</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
       <c r="V74">
         <f>(I74-O74)^2+(J74-P74)^2+(K74-Q74)^2</f>
         <v/>
@@ -11063,22 +10920,11 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U75" t="n">
-        <v>6.49</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
       <c r="V75">
         <f>(I75-O75)^2+(J75-P75)^2+(K75-Q75)^2</f>
         <v/>
@@ -11151,22 +10997,11 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U76" t="n">
-        <v>6.49</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
       <c r="V76">
         <f>(I76-O76)^2+(J76-P76)^2+(K76-Q76)^2</f>
         <v/>
@@ -11239,22 +11074,11 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U77" t="n">
-        <v>6.49</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
       <c r="V77">
         <f>(I77-O77)^2+(J77-P77)^2+(K77-Q77)^2</f>
         <v/>
@@ -11635,22 +11459,11 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U82" t="n">
-        <v>6.7</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
       <c r="V82">
         <f>(I82-O82)^2+(J82-P82)^2+(K82-Q82)^2</f>
         <v/>
@@ -11723,22 +11536,11 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U83" t="n">
-        <v>6.7</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
       <c r="V83">
         <f>(I83-O83)^2+(J83-P83)^2+(K83-Q83)^2</f>
         <v/>
@@ -11811,22 +11613,11 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U84" t="n">
-        <v>6.7</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
       <c r="V84">
         <f>(I84-O84)^2+(J84-P84)^2+(K84-Q84)^2</f>
         <v/>
@@ -11899,22 +11690,11 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U85" t="n">
-        <v>6.7</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
       <c r="V85">
         <f>(I85-O85)^2+(J85-P85)^2+(K85-Q85)^2</f>
         <v/>
@@ -11987,22 +11767,11 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U86" t="n">
-        <v>9.94</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
       <c r="V86">
         <f>(I86-O86)^2+(J86-P86)^2+(K86-Q86)^2</f>
         <v/>
@@ -12075,22 +11844,11 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U87" t="n">
-        <v>9.94</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
       <c r="V87">
         <f>(I87-O87)^2+(J87-P87)^2+(K87-Q87)^2</f>
         <v/>
@@ -12163,22 +11921,11 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U88" t="n">
-        <v>9.94</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
       <c r="V88">
         <f>(I88-O88)^2+(J88-P88)^2+(K88-Q88)^2</f>
         <v/>
@@ -12251,22 +11998,11 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U89" t="n">
-        <v>9.94</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
       <c r="V89">
         <f>(I89-O89)^2+(J89-P89)^2+(K89-Q89)^2</f>
         <v/>
@@ -12339,22 +12075,11 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U90" t="n">
-        <v>8.44</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
       <c r="V90">
         <f>(I90-O90)^2+(J90-P90)^2+(K90-Q90)^2</f>
         <v/>
@@ -12427,22 +12152,11 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U91" t="n">
-        <v>8.44</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
       <c r="V91">
         <f>(I91-O91)^2+(J91-P91)^2+(K91-Q91)^2</f>
         <v/>
@@ -12515,22 +12229,11 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U92" t="n">
-        <v>8.44</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
       <c r="V92">
         <f>(I92-O92)^2+(J92-P92)^2+(K92-Q92)^2</f>
         <v/>
@@ -12603,22 +12306,11 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U93" t="n">
-        <v>8.44</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
       <c r="V93">
         <f>(I93-O93)^2+(J93-P93)^2+(K93-Q93)^2</f>
         <v/>
@@ -12691,22 +12383,11 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U94" t="n">
-        <v>8.550000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
       <c r="V94">
         <f>(I94-O94)^2+(J94-P94)^2+(K94-Q94)^2</f>
         <v/>
@@ -12779,22 +12460,11 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U95" t="n">
-        <v>8.550000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
       <c r="V95">
         <f>(I95-O95)^2+(J95-P95)^2+(K95-Q95)^2</f>
         <v/>
@@ -12867,22 +12537,11 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U96" t="n">
-        <v>8.550000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
       <c r="V96">
         <f>(I96-O96)^2+(J96-P96)^2+(K96-Q96)^2</f>
         <v/>
@@ -12955,22 +12614,11 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U97" t="n">
-        <v>8.550000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
       <c r="V97">
         <f>(I97-O97)^2+(J97-P97)^2+(K97-Q97)^2</f>
         <v/>
@@ -13395,22 +13043,11 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U102" t="n">
-        <v>10.36</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
       <c r="V102">
         <f>(I102-O102)^2+(J102-P102)^2+(K102-Q102)^2</f>
         <v/>
@@ -13483,22 +13120,11 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U103" t="n">
-        <v>10.36</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
       <c r="V103">
         <f>(I103-O103)^2+(J103-P103)^2+(K103-Q103)^2</f>
         <v/>
@@ -13571,22 +13197,11 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T104" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U104" t="n">
-        <v>10.36</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
       <c r="V104">
         <f>(I104-O104)^2+(J104-P104)^2+(K104-Q104)^2</f>
         <v/>
@@ -13659,22 +13274,11 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T105" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U105" t="n">
-        <v>10.36</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
       <c r="V105">
         <f>(I105-O105)^2+(J105-P105)^2+(K105-Q105)^2</f>
         <v/>
@@ -14407,22 +14011,11 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="T114" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U114" t="n">
-        <v>5.39</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
       <c r="V114">
         <f>(I114-O114)^2+(J114-P114)^2+(K114-Q114)^2</f>
         <v/>
@@ -14495,22 +14088,11 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="T115" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U115" t="n">
-        <v>5.39</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
       <c r="V115">
         <f>(I115-O115)^2+(J115-P115)^2+(K115-Q115)^2</f>
         <v/>
@@ -14583,22 +14165,11 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U116" t="n">
-        <v>5.39</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
       <c r="V116">
         <f>(I116-O116)^2+(J116-P116)^2+(K116-Q116)^2</f>
         <v/>
@@ -14671,22 +14242,11 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="T117" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U117" t="n">
-        <v>5.39</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
       <c r="V117">
         <f>(I117-O117)^2+(J117-P117)^2+(K117-Q117)^2</f>
         <v/>
@@ -15419,22 +14979,11 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U126" t="n">
-        <v>9.609999999999999</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr"/>
       <c r="V126">
         <f>(I126-O126)^2+(J126-P126)^2+(K126-Q126)^2</f>
         <v/>
@@ -15507,22 +15056,11 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U127" t="n">
-        <v>9.609999999999999</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr"/>
       <c r="V127">
         <f>(I127-O127)^2+(J127-P127)^2+(K127-Q127)^2</f>
         <v/>
@@ -15595,22 +15133,11 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U128" t="n">
-        <v>9.609999999999999</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr"/>
       <c r="V128">
         <f>(I128-O128)^2+(J128-P128)^2+(K128-Q128)^2</f>
         <v/>
@@ -15683,22 +15210,11 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="T129" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U129" t="n">
-        <v>9.609999999999999</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr"/>
       <c r="V129">
         <f>(I129-O129)^2+(J129-P129)^2+(K129-Q129)^2</f>
         <v/>
@@ -16123,22 +15639,11 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U134" t="n">
-        <v>9.210000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr"/>
       <c r="V134">
         <f>(I134-O134)^2+(J134-P134)^2+(K134-Q134)^2</f>
         <v/>
@@ -16211,22 +15716,11 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="T135" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U135" t="n">
-        <v>9.210000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
       <c r="V135">
         <f>(I135-O135)^2+(J135-P135)^2+(K135-Q135)^2</f>
         <v/>
@@ -16299,22 +15793,11 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="T136" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U136" t="n">
-        <v>9.210000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr"/>
       <c r="V136">
         <f>(I136-O136)^2+(J136-P136)^2+(K136-Q136)^2</f>
         <v/>
@@ -16387,22 +15870,11 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="T137" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U137" t="n">
-        <v>9.210000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
       <c r="V137">
         <f>(I137-O137)^2+(J137-P137)^2+(K137-Q137)^2</f>
         <v/>
@@ -17487,22 +16959,11 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="T150" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U150" t="n">
-        <v>9.640000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr"/>
       <c r="V150">
         <f>(I150-O150)^2+(J150-P150)^2+(K150-Q150)^2</f>
         <v/>
@@ -17575,22 +17036,11 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="T151" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U151" t="n">
-        <v>9.640000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr"/>
       <c r="V151">
         <f>(I151-O151)^2+(J151-P151)^2+(K151-Q151)^2</f>
         <v/>
@@ -17663,22 +17113,11 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="T152" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U152" t="n">
-        <v>9.640000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr"/>
+      <c r="T152" t="inlineStr"/>
       <c r="V152">
         <f>(I152-O152)^2+(J152-P152)^2+(K152-Q152)^2</f>
         <v/>
@@ -17751,22 +17190,11 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="T153" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U153" t="n">
-        <v>9.640000000000001</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="inlineStr"/>
       <c r="V153">
         <f>(I153-O153)^2+(J153-P153)^2+(K153-Q153)^2</f>
         <v/>
@@ -18499,22 +17927,11 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T162" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U162" t="n">
-        <v>7.66</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr"/>
       <c r="V162">
         <f>(I162-O162)^2+(J162-P162)^2+(K162-Q162)^2</f>
         <v/>
@@ -18587,22 +18004,11 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T163" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U163" t="n">
-        <v>7.66</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr"/>
+      <c r="T163" t="inlineStr"/>
       <c r="V163">
         <f>(I163-O163)^2+(J163-P163)^2+(K163-Q163)^2</f>
         <v/>
@@ -18675,22 +18081,11 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T164" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U164" t="n">
-        <v>7.66</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr"/>
+      <c r="T164" t="inlineStr"/>
       <c r="V164">
         <f>(I164-O164)^2+(J164-P164)^2+(K164-Q164)^2</f>
         <v/>
@@ -18763,22 +18158,11 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="T165" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U165" t="n">
-        <v>7.66</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="inlineStr"/>
       <c r="V165">
         <f>(I165-O165)^2+(J165-P165)^2+(K165-Q165)^2</f>
         <v/>
@@ -20215,22 +19599,11 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="T182" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U182" t="n">
-        <v>11.26</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr"/>
+      <c r="T182" t="inlineStr"/>
       <c r="V182">
         <f>(I182-O182)^2+(J182-P182)^2+(K182-Q182)^2</f>
         <v/>
@@ -20303,22 +19676,11 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="T183" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U183" t="n">
-        <v>11.26</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr"/>
+      <c r="T183" t="inlineStr"/>
       <c r="V183">
         <f>(I183-O183)^2+(J183-P183)^2+(K183-Q183)^2</f>
         <v/>
@@ -20391,22 +19753,11 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="T184" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U184" t="n">
-        <v>11.26</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr"/>
+      <c r="T184" t="inlineStr"/>
       <c r="V184">
         <f>(I184-O184)^2+(J184-P184)^2+(K184-Q184)^2</f>
         <v/>
@@ -20479,22 +19830,11 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="T185" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U185" t="n">
-        <v>11.26</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr"/>
+      <c r="T185" t="inlineStr"/>
       <c r="V185">
         <f>(I185-O185)^2+(J185-P185)^2+(K185-Q185)^2</f>
         <v/>
@@ -20919,22 +20259,11 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="T190" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U190" t="n">
-        <v>7.87</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr"/>
+      <c r="T190" t="inlineStr"/>
       <c r="V190">
         <f>(I190-O190)^2+(J190-P190)^2+(K190-Q190)^2</f>
         <v/>
@@ -21007,22 +20336,11 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="T191" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U191" t="n">
-        <v>7.87</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr"/>
+      <c r="T191" t="inlineStr"/>
       <c r="V191">
         <f>(I191-O191)^2+(J191-P191)^2+(K191-Q191)^2</f>
         <v/>
@@ -21095,22 +20413,11 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="T192" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U192" t="n">
-        <v>7.87</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr"/>
+      <c r="T192" t="inlineStr"/>
       <c r="V192">
         <f>(I192-O192)^2+(J192-P192)^2+(K192-Q192)^2</f>
         <v/>
@@ -21183,22 +20490,11 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="T193" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U193" t="n">
-        <v>7.87</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr"/>
+      <c r="T193" t="inlineStr"/>
       <c r="V193">
         <f>(I193-O193)^2+(J193-P193)^2+(K193-Q193)^2</f>
         <v/>
@@ -23999,22 +23295,11 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T226" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U226" t="n">
-        <v>9.609999999999999</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr"/>
+      <c r="T226" t="inlineStr"/>
       <c r="V226">
         <f>(I226-O226)^2+(J226-P226)^2+(K226-Q226)^2</f>
         <v/>
@@ -24087,22 +23372,11 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T227" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U227" t="n">
-        <v>9.609999999999999</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr"/>
+      <c r="T227" t="inlineStr"/>
       <c r="V227">
         <f>(I227-O227)^2+(J227-P227)^2+(K227-Q227)^2</f>
         <v/>
@@ -24175,22 +23449,11 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T228" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U228" t="n">
-        <v>9.609999999999999</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr"/>
+      <c r="T228" t="inlineStr"/>
       <c r="V228">
         <f>(I228-O228)^2+(J228-P228)^2+(K228-Q228)^2</f>
         <v/>
@@ -24263,22 +23526,11 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="T229" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U229" t="n">
-        <v>9.609999999999999</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr"/>
+      <c r="T229" t="inlineStr"/>
       <c r="V229">
         <f>(I229-O229)^2+(J229-P229)^2+(K229-Q229)^2</f>
         <v/>
@@ -24351,22 +23603,11 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T230" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U230" t="n">
-        <v>7.08</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr"/>
+      <c r="T230" t="inlineStr"/>
       <c r="V230">
         <f>(I230-O230)^2+(J230-P230)^2+(K230-Q230)^2</f>
         <v/>
@@ -24439,22 +23680,11 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T231" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U231" t="n">
-        <v>7.08</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr"/>
+      <c r="T231" t="inlineStr"/>
       <c r="V231">
         <f>(I231-O231)^2+(J231-P231)^2+(K231-Q231)^2</f>
         <v/>
@@ -24527,22 +23757,11 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T232" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U232" t="n">
-        <v>7.08</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr"/>
+      <c r="T232" t="inlineStr"/>
       <c r="V232">
         <f>(I232-O232)^2+(J232-P232)^2+(K232-Q232)^2</f>
         <v/>
@@ -24615,22 +23834,11 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="T233" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U233" t="n">
-        <v>7.08</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr"/>
+      <c r="T233" t="inlineStr"/>
       <c r="V233">
         <f>(I233-O233)^2+(J233-P233)^2+(K233-Q233)^2</f>
         <v/>
@@ -26067,22 +25275,11 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="T250" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U250" t="n">
-        <v>8.5</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr"/>
+      <c r="T250" t="inlineStr"/>
       <c r="V250">
         <f>(I250-O250)^2+(J250-P250)^2+(K250-Q250)^2</f>
         <v/>
@@ -26155,22 +25352,11 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="T251" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U251" t="n">
-        <v>8.5</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr"/>
+      <c r="T251" t="inlineStr"/>
       <c r="V251">
         <f>(I251-O251)^2+(J251-P251)^2+(K251-Q251)^2</f>
         <v/>
@@ -26243,22 +25429,11 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="T252" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U252" t="n">
-        <v>8.5</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr"/>
+      <c r="T252" t="inlineStr"/>
       <c r="V252">
         <f>(I252-O252)^2+(J252-P252)^2+(K252-Q252)^2</f>
         <v/>
@@ -26331,22 +25506,11 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>pick</t>
-        </is>
-      </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="T253" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="U253" t="n">
-        <v>8.5</v>
-      </c>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr"/>
+      <c r="T253" t="inlineStr"/>
       <c r="V253">
         <f>(I253-O253)^2+(J253-P253)^2+(K253-Q253)^2</f>
         <v/>
